--- a/output/june_2026_full_result.xlsx
+++ b/output/june_2026_full_result.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S69"/>
+  <dimension ref="A1:S62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,25 +528,30 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>323462</v>
+        <v>323533</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://mindbox.pipedrive.com/deal/323462</t>
+          <t>https://mindbox.pipedrive.com/deal/323533</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ncsemena.ru</t>
+          <t>Сделка docstarclub.ru</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Персона: Дубль</t>
+          <t>Midmarket: выбрали конкурента, текущий стек или сделают сами – напиши кому в Коммент при проигрыше</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>говорят, что все реализовали на своих ии-агентах, собственник не увидел ничего, что у них не реализовано</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>492</v>
+        <v>385</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -555,74 +560,52 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>CDP / база клиентов: не упоминался | Email: используют, но не определили стек | SMS: не используют (дорого) | Мессенджеры: используют, но не определили стек | Мобильные пуши / In-app: не упоминался | Чат-боты: In-house решение | Лояльность: используют, но не определили стек | Сценарии и триггеры: используют, но не определили стек | Персонализация сайта: используют, но не определили стек | Квизы и опросы: не упоминался | ML рекомендации: In-house решение | Аналитика и A/B тесты: по базе — In-house решение (конверсия посетителей в заказы), по ПЛ — не упоминался, по рекламе — не упоминался, A/B тесты — нет</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Клиент сформулировал цели.
-Метрики:
-- (основная) Рост конверсии посетителей в заказы | Кто: руководитель (предположительно)
-- Рост конверсии на всех этапах воронки (повторные покупки, средний чек, первый заказ) | Кто: руководитель (предположительно) | (подтверждена, изначально предложена менеджером)
-Проекты/задачи:
-- Увеличение посещений сайта и рост базы клиентов → для компенсации оттока трафика в маркетплейсы | Кто: руководитель (предположительно)
-Общие проблемы:
-- (основная) Отток клиентов из e-commerce в маркетплейсы — продолжается последние 3–4 года, общее количество посещений падает | Кто: руководитель (предположительно)</t>
+          <t>CDP / база клиентов: Chatium, ClickHouse, GetCourse | Email: GetCourse | SMS: используют, но не определили стек | Мессенджеры: In-house решение (через Chatium) | Мобильные пуши / In-app: не упоминался | Чат-боты: In-house решение (нейросеть) | Лояльность: не упоминался | Сценарии и триггеры: In-house решение (через Chatium + GetCourse) | Персонализация сайта: In-house решение | Квизы и опросы: не упоминался | ML рекомендации: In-house решение (нейросеть) | Аналитика и A/B тесты: по базе — In-house решение (когортный анализ), по ПЛ — не упоминался, по рекламе — не упоминался, A/B тесты — есть (ручные)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Маркетолог, Руководитель e-commerce, Руководитель направления</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>[Аналитика и A/B тесты] Нет глубокой аналитики по этапам воронки — смотрят только общую конверсию посетителей в заказы, конкретные этапы не прослеживают
-«мы, к сожалению, так глубоко на это не смотрим. Мы, в принципе, смотрим источники, где мы рекламируемся, как человек приходит. И смотрим в целом конверсию от посетителей в заказы... конкретные этапы воронки мы не прослеживаем»
-[Персонализация сайта] Попапы раздражают клиентов, особенно на мобильной версии — пришлось отключить из-за жалоб
-«клиенты от большого количества попапов очень сильно жалуются, поэтому мы с обратной статистикой их отключили... особенно на мобильной версии, это закрывает полностью экран, а клиентов раздражает»
-[SMS] SMS не используют из-за высокой стоимости
-«СМС дорого отправлять»</t>
+          <t>Генеральный директор</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-06-15T15:16:47Z</t>
+          <t>2026-06-18T15:00:24Z</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>Нецелевой</t>
+          <t>Конкурент</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>Дубль персоны/сделки</t>
+          <t>Свой кастом на Chatium + ИИ-агенты, всё закрывают сами</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>Коммент пуст — по указанной причине/заметкам.</t>
+          <t>Коммент при проигрыше: «говорят, что все реализовали на своих ии-агентах, собственник не увидел ничего, что у них не реализовано».</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>323533</v>
+        <v>324171</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://mindbox.pipedrive.com/deal/323533</t>
+          <t>https://mindbox.pipedrive.com/deal/324171</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Сделка docstarclub.ru</t>
+          <t>Сделка swimrocket.ru</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -632,30 +615,20 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>говорят, что все реализовали на своих ии-агентах, собственник не увидел ничего, что у них не реализовано</t>
+          <t>1С-Фитнеса достаточно</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>lost</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>CDP / база клиентов: Chatium, ClickHouse, GetCourse | Email: GetCourse | SMS: используют, но не определили стек | Мессенджеры: In-house решение (через Chatium) | Мобильные пуши / In-app: не упоминался | Чат-боты: In-house решение (нейросеть) | Лояльность: не упоминался | Сценарии и триггеры: In-house решение (через Chatium + GetCourse) | Персонализация сайта: In-house решение | Квизы и опросы: не упоминался | ML рекомендации: In-house решение (нейросеть) | Аналитика и A/B тесты: по базе — In-house решение (когортный анализ), по ПЛ — не упоминался, по рекламе — не упоминался, A/B тесты — есть (ручные)</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Генеральный директор</t>
-        </is>
-      </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-06-18T15:00:24Z</t>
+          <t>2026-06-17T12:44:06Z</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
@@ -665,164 +638,53 @@
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>Свой кастом на Chatium + ИИ-агенты, всё закрывают сами</t>
+          <t>1С-Фитнеса достаточно</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>Коммент при проигрыше: «говорят, что все реализовали на своих ии-агентах, собственник не увидел ничего, что у них не реализовано».</t>
+          <t>Коммент при проигрыше: «1С-Фитнеса достаточно».</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>324171</v>
+        <v>327711</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://mindbox.pipedrive.com/deal/324171</t>
+          <t>https://mindbox.pipedrive.com/deal/327711</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Сделка swimrocket.ru</t>
+          <t>Сделка gaga.ru</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Midmarket: выбрали конкурента, текущий стек или сделают сами – напиши кому в Коммент при проигрыше</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1С-Фитнеса достаточно</t>
+          <t>Midmarket: SS, так как маленькая база</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>lost</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2026-06-17T12:44:06Z</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>Конкурент</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t>1С-Фитнеса достаточно</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t>Коммент при проигрыше: «1С-Фитнеса достаточно».</t>
-        </is>
-      </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>324933</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>https://mindbox.pipedrive.com/deal/324933</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>animationschool.ru</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Персона: Дубль</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>449</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2026-06-22T08:08:27Z</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t>Нецелевой</t>
-        </is>
-      </c>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t>Дубль персоны/сделки</t>
-        </is>
-      </c>
-      <c r="R5" s="3" t="inlineStr">
-        <is>
-          <t>Коммент пуст — по указанной причине/заметкам.</t>
-        </is>
-      </c>
-      <c r="S5" s="3" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>327711</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>https://mindbox.pipedrive.com/deal/327711</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Сделка gaga.ru</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Midmarket: SS, так как маленькая база</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>385</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>CDP / база клиентов: In-house решение | Email: Unisender | SMS: не упоминался | Мессенджеры: планируют | Мобильные пуши / In-app: не упоминался | Чат-боты: планируют | Лояльность: In-house решение | Сценарии и триггеры: не используют | Персонализация сайта: не упоминался | Квизы и опросы: не упоминался | ML рекомендации: не упоминался | Аналитика и A/B тесты: по базе — In-house решение (ограниченная), по ПЛ — не упоминался, по рекламе — не упоминался, A/B тесты — нет</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Клиент сформулировал цели.
 Проекты/задачи:
@@ -838,12 +700,12 @@
 - Активная открывающая база очень мала (~10-15 тыс.) при общей базе ~180 тыс. | Кто: Руководитель маркетинга</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Руководитель маркетинга, Email-маркетолог</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>[CDP / база клиентов] Самописный сайт устарел и вызывает опасения при внедрении новых инструментов
 «у нас довольно грустный древний самописный сайт... это вот такой для нас фактор тревоги, если что-то новое на него внедрять, как он вообще это потянет»
@@ -857,24 +719,140 @@
 «мы эту базу просто выгружаем ручками, обновляем, загружаем и радостно массово на них шлем»</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2026-06-18T15:15:41Z</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>Указана причина SS</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>Коммент пуст — по указанной причине/заметкам.</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>329058</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://mindbox.pipedrive.com/deal/329058</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Сделка atlas.ru</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Midmarket: SS, так как маленькая база</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>не окупятся</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>385</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2026-06-10T07:02:25Z</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>Указана SS; «не окупятся»</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>Коммент при проигрыше: «не окупятся».</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>336723</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://mindbox.pipedrive.com/deal/336723</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Сделка grandtrain.ru</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Midmarket: не нашел подходящей причины проигрыша – напиши свою в Коммент при проигрыше</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>резко урезали бюджеты, отложили на осень</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>386</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-06-18T15:15:41Z</t>
+          <t>2026-06-25T13:45:10Z</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>Клиенту дорого, хотя база норм</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>Указана причина SS</t>
+          <t>Резко урезали бюджеты, отложили на осень</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>Коммент пуст — по указанной причине/заметкам.</t>
+          <t>Коммент при проигрыше: «резко урезали бюджеты, отложили на осень».</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
@@ -885,26 +863,21 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>329058</v>
+        <v>339774</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://mindbox.pipedrive.com/deal/329058</t>
+          <t>https://mindbox.pipedrive.com/deal/339774</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Сделка atlas.ru</t>
+          <t>Сделка pizzapaolo.ru</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Midmarket: SS, так как маленькая база</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>не окупятся</t>
+          <t>Midmarket: не могу получить ответ от клиента</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -915,246 +888,82 @@
           <t>lost</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2026-06-10T07:02:25Z</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr">
-        <is>
-          <t>SS</t>
-        </is>
-      </c>
-      <c r="Q7" s="3" t="inlineStr">
-        <is>
-          <t>Указана SS; «не окупятся»</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="inlineStr">
-        <is>
-          <t>Коммент при проигрыше: «не окупятся».</t>
-        </is>
-      </c>
-      <c r="S7" s="3" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>336723</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>https://mindbox.pipedrive.com/deal/336723</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Сделка grandtrain.ru</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Midmarket: не нашел подходящей причины проигрыша – напиши свою в Коммент при проигрыше</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>резко урезали бюджеты, отложили на осень</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>386</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2026-06-25T13:45:10Z</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr">
-        <is>
-          <t>Клиенту дорого, хотя база норм</t>
-        </is>
-      </c>
-      <c r="Q8" s="3" t="inlineStr">
-        <is>
-          <t>Резко урезали бюджеты, отложили на осень</t>
-        </is>
-      </c>
-      <c r="R8" s="3" t="inlineStr">
-        <is>
-          <t>Коммент при проигрыше: «резко урезали бюджеты, отложили на осень».</t>
-        </is>
-      </c>
-      <c r="S8" s="3" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>337124</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>https://mindbox.pipedrive.com/deal/337124</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>metrofitness.ru</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Персона: Дубль</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>386</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2026-06-15T15:14:40Z</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="inlineStr">
-        <is>
-          <t>Нецелевой</t>
-        </is>
-      </c>
-      <c r="Q9" s="3" t="inlineStr">
-        <is>
-          <t>Дубль персоны/сделки</t>
-        </is>
-      </c>
-      <c r="R9" s="3" t="inlineStr">
-        <is>
-          <t>Коммент пуст — по указанной причине/заметкам.</t>
-        </is>
-      </c>
-      <c r="S9" s="3" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>339774</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://mindbox.pipedrive.com/deal/339774</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Сделка pizzapaolo.ru</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Midmarket: не могу получить ответ от клиента</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>385</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>CDP / база клиентов: не упоминался | Email: не упоминался | SMS: не упоминался | Мессенджеры: не упоминался | Мобильные пуши / In-app: не упоминался | Чат-боты: не упоминался | Лояльность: Iiko (встроенная), In-house решение | Сценарии и триггеры: не упоминался | Персонализация сайта: не упоминался | Квизы и опросы: не упоминался | ML рекомендации: не упоминался | Аналитика и A/B тесты: по базе — не упоминался, по ПЛ — не упоминался, по рекламе — не упоминался, A/B тесты — не упоминался</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Клиент не сформулировал явных целей. Ниже фоновые проблемы и ограничения.
 Общие проблемы:
 - Отсутствие маркетинговой экспертизы и опыта работы с CRM-маркетингом — клиент не думал о персонализации и анализе клиентов | Кто: роль не определена (предположительно управляющий)</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>2026-06-02T14:01:41Z</t>
         </is>
       </c>
-      <c r="P10" s="3" t="inlineStr">
+      <c r="P7" s="3" t="inlineStr">
         <is>
           <t>Клиент перестал отвечать</t>
         </is>
       </c>
-      <c r="Q10" s="3" t="inlineStr">
+      <c r="Q7" s="3" t="inlineStr">
         <is>
           <t>Нет ответа</t>
         </is>
       </c>
-      <c r="R10" s="3" t="inlineStr">
+      <c r="R7" s="3" t="inlineStr">
         <is>
           <t>Коммент пуст — по указанной причине/заметкам.</t>
         </is>
       </c>
-      <c r="S10" s="3" t="inlineStr">
+      <c r="S7" s="3" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
+    <row r="8">
+      <c r="A8" t="n">
         <v>342605</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>https://mindbox.pipedrive.com/deal/342605</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>brusnikabrand.com</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Midmarket: выбрали конкурента, текущий стек или сделают сами – напиши кому в Коммент при проигрыше</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>cсобственница не согласовала, остались на своих инструментах</t>
         </is>
       </c>
-      <c r="H11" t="n">
+      <c r="H8" t="n">
         <v>386</v>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>CDP / база клиентов: In-house решение, 1С | Email: Sensei | SMS: не упоминался | Мессенджеры: не упоминался | Мобильные пуши / In-app: не упоминался | Чат-боты: не упоминался | Лояльность: In-house решение | Сценарии и триггеры: Sensei | Персонализация сайта: не упоминался | Квизы и опросы: не упоминался | ML рекомендации: не упоминался | Аналитика и A/B тесты: по базе — In-house решение, по ПЛ — не упоминался, по рекламе — не упоминался, A/B тесты — не упоминался</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Клиент сформулировал цели.
 Проекты/задачи:
@@ -1167,19 +976,19 @@
 - Стандартный функционал 1С ограничен — нет возможности фильтровать покупателей по активности без привлечения специалиста | Кто: руководитель интернет-магазина</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Руководитель интернет-магазина</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>[Сценарии и триггеры] Клиент считает, что базовые триггеры по сайту можно реализовать текущим инструментом
 «Но это мы можем стандартно сделать. В каком-нибудь SendPulse.»
 Стоимость: Клиент знает прежние цены Mindbox (156–170 тыс.), посчитала окупаемость при минимальном тарифе 180 тыс./мес и выручке только интернет-магазина — пришла к выводу, что дорого. Конкретную стоимость текущего стека не назвала. Цитата: «Это я 900 потрачу, миллион 250 я сделаю. Соответственно, наварю я только 350 тысяч. И то это 35 месяцев. Я это сделаю. Дорого, понятно.»</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>[CDP / база клиентов] Базы онлайн и оффлайн не объединены
 «У нас, например, не совмещена база оффлайн и онлайн.»
@@ -1197,65 +1006,65 @@
 «Ну, в стандартном функционале нет. Если к специалисту обратиться, возможно.»</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>2026-06-09T16:49:43Z</t>
         </is>
       </c>
-      <c r="P11" s="3" t="inlineStr">
+      <c r="P8" s="3" t="inlineStr">
         <is>
           <t>Руководитель заблокировал решение</t>
         </is>
       </c>
-      <c r="Q11" s="3" t="inlineStr">
+      <c r="Q8" s="3" t="inlineStr">
         <is>
           <t>Собственница не согласовала (остались на своих инструментах)</t>
         </is>
       </c>
-      <c r="R11" s="3" t="inlineStr">
+      <c r="R8" s="3" t="inlineStr">
         <is>
           <t>Коммент при проигрыше: «cсобственница не согласовала, остались на своих инструментах».</t>
         </is>
       </c>
-      <c r="S11" s="3" t="inlineStr">
+      <c r="S8" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
+    <row r="9">
+      <c r="A9" t="n">
         <v>344907</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>https://mindbox.pipedrive.com/deal/344907</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>svetlux.ru</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>OPA: Делают сами</t>
         </is>
       </c>
-      <c r="H12" t="n">
+      <c r="H9" t="n">
         <v>385</v>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>CDP / база клиентов: используют, но не определили стек | Email: используют, но не определили стек | SMS: используют, но не определили стек | Мессенджеры: не упоминался | Мобильные пуши / In-app: не упоминался | Чат-боты: не упоминался | Лояльность: акции и промокоды — используют, но не определили стек; программа лояльности — нет | Сценарии и триггеры: используют, но не определили стек | Персонализация сайта: используют, но не определили стек | Квизы и опросы: не упоминался | ML рекомендации: используют, но не определили стек | Аналитика и A/B тесты: по рекламе — используют, но не определили стек, по базе — не упоминался, по ПЛ — не упоминался, A/B тесты — не упоминался</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Клиент сформулировал цели.
 Метрики:
@@ -1271,12 +1080,12 @@
 - Часть клиентов ушла на маркетплейсы: «те люди, которые просто заказывали настольную лампу какую-то себе или там бра докупали, они большинство уже ушли на marketplace» | Кто: партнёр/генеральный директор</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Собственник</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>[Email / Сценарии и триггеры] Рассылки персонализированы — отправляются рекомендованные товары на основе интересов клиента
 «Рассылки у нас также используются и присылаются именно рекомендованные товары, исходя из того, чем человек интересовался. Соответственно, ему приходят письма... эта информационная рассылка у нас тоже присутствует.»
@@ -1291,7 +1100,7 @@
 Стоимость: Клиент выразил сомнение в окупаемости Mindbox при 183 000 ₽/мес с НДС. При инкременте ~5% «дай бог, будет окупаемость». Компания на стадии экономии и оптимизации расходов, спад продаж. Конкретную стоимость текущего стека не назвал.</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>[SMS] SMS-рассылки с промокодами оказались неэффективными — тестировали два года без результата
 «Но это не работает, я могу вам так сказать. Мы два года это пробовали, а результата ноль.»
@@ -1301,24 +1110,198 @@
 «единственное, что мы, может быть, не пользуемся, не используем и, наверное, не пробовали, это программа лояльности»</t>
         </is>
       </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2026-06-22T10:15:39Z</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>Конкурент</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>Делают сами, механики уже реализуют своими силами + режим экономии</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>Коммент пуст — по указанной причине/заметкам.</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>352815</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://mindbox.pipedrive.com/deal/352815</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Сделка polza.ru Назначена встреча</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Midmarket: выбрали конкурента, текущий стек или сделают сами – напиши кому в Коммент при проигрыше</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Нет драйвера проекта</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>492</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2026-06-18T07:23:19Z</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>Не заинтересовали ЛВР</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>Нет драйвера проекта, нулевая экспертиза по маркетингу, ушли в тишину</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>Коммент при проигрыше: «Нет драйвера проекта».</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>357554</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://mindbox.pipedrive.com/deal/357554</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Medsyst</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Midmarket: не могу получить ответ от клиента</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>перенос общения на май</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>386</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2026-06-23T11:12:45Z</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>Попросили отложить</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>Перенос общения на май</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>Коммент при проигрыше: «перенос общения на май».</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>358655</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://mindbox.pipedrive.com/deal/358655</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>hyperpc.ru</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Midmarket: не готовы интегрироваться – напиши почему в Коммент при проигрыше</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>переходят на новую ерп, переносим</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>390</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-06-22T10:15:39Z</t>
+          <t>2026-06-17T09:00:38Z</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>Конкурент</t>
+          <t>Интеграция</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>Делают сами, механики уже реализуют своими силами + режим экономии</t>
+          <t>Переход на новую ERP — переносят</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>Коммент пуст — по указанной причине/заметкам.</t>
+          <t>Коммент при проигрыше: «переходят на новую ерп, переносим».</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
@@ -1329,16 +1312,16 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>352815</v>
+        <v>361438</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://mindbox.pipedrive.com/deal/352815</t>
+          <t>https://mindbox.pipedrive.com/deal/361438</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Сделка polza.ru Назначена встреча</t>
+          <t>sotkaonline.ru Назначена встреча</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1348,11 +1331,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Нет драйвера проекта</t>
+          <t>у нас чокнутая тарификация на 60 ботов, они на сейлботе раз в 10 дешевле делаюь</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>492</v>
+        <v>449</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1361,242 +1344,68 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-06-18T07:23:19Z</t>
+          <t>2026-06-02T10:31:17Z</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>Не заинтересовали ЛВР</t>
+          <t>Конкурент</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>Нет драйвера проекта, нулевая экспертиза по маркетингу, ушли в тишину</t>
+          <t>SaleBot (на 60 ботов в ~10 раз дешевле)</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>Коммент при проигрыше: «Нет драйвера проекта».</t>
+          <t>Коммент при проигрыше: «у нас чокнутая тарификация на 60 ботов, они на сейлботе раз в 10 дешевле делаюь».</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>357554</v>
+        <v>364819</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://mindbox.pipedrive.com/deal/357554</t>
+          <t>https://mindbox.pipedrive.com/deal/364819</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Medsyst</t>
+          <t>самозанятые.рф</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Midmarket: не могу получить ответ от клиента</t>
+          <t>Midmarket: не нашел подходящей причины проигрыша – напиши свою в Коммент при проигрыше</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>перенос общения на май</t>
+          <t>внутренние перестановки, пока вектор на другое, вернусь позже</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>386</v>
+        <v>449</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>lost</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2026-06-23T11:12:45Z</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="inlineStr">
-        <is>
-          <t>Попросили отложить</t>
-        </is>
-      </c>
-      <c r="Q14" s="3" t="inlineStr">
-        <is>
-          <t>Перенос общения на май</t>
-        </is>
-      </c>
-      <c r="R14" s="3" t="inlineStr">
-        <is>
-          <t>Коммент при проигрыше: «перенос общения на май».</t>
-        </is>
-      </c>
-      <c r="S14" s="3" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>358655</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>https://mindbox.pipedrive.com/deal/358655</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>hyperpc.ru</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Midmarket: не готовы интегрироваться – напиши почему в Коммент при проигрыше</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>переходят на новую ерп, переносим</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>390</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2026-06-17T09:00:38Z</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="inlineStr">
-        <is>
-          <t>Интеграция</t>
-        </is>
-      </c>
-      <c r="Q15" s="3" t="inlineStr">
-        <is>
-          <t>Переход на новую ERP — переносят</t>
-        </is>
-      </c>
-      <c r="R15" s="3" t="inlineStr">
-        <is>
-          <t>Коммент при проигрыше: «переходят на новую ерп, переносим».</t>
-        </is>
-      </c>
-      <c r="S15" s="3" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>361438</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>https://mindbox.pipedrive.com/deal/361438</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>sotkaonline.ru Назначена встреча</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Midmarket: выбрали конкурента, текущий стек или сделают сами – напиши кому в Коммент при проигрыше</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>у нас чокнутая тарификация на 60 ботов, они на сейлботе раз в 10 дешевле делаюь</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>449</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2026-06-02T10:31:17Z</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="inlineStr">
-        <is>
-          <t>Конкурент</t>
-        </is>
-      </c>
-      <c r="Q16" s="3" t="inlineStr">
-        <is>
-          <t>SaleBot (на 60 ботов в ~10 раз дешевле)</t>
-        </is>
-      </c>
-      <c r="R16" s="3" t="inlineStr">
-        <is>
-          <t>Коммент при проигрыше: «у нас чокнутая тарификация на 60 ботов, они на сейлботе раз в 10 дешевле делаюь».</t>
-        </is>
-      </c>
-      <c r="S16" s="3" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>364819</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>https://mindbox.pipedrive.com/deal/364819</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>самозанятые.рф</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Midmarket: не нашел подходящей причины проигрыша – напиши свою в Коммент при проигрыше</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>внутренние перестановки, пока вектор на другое, вернусь позже</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>449</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>CDP / база клиентов: не упоминался | Email: не упоминался | SMS: используют, но не определили стек | Мессенджеры: не упоминался | Мобильные пуши / In-app: не используют (только in-app колокольчик уведомлений) | Чат-боты: используют, но не определили стек | Лояльность: не упоминался | Сценарии и триггеры: не упоминался | Персонализация сайта: не упоминался | Квизы и опросы: не упоминался | ML рекомендации: не упоминался | Аналитика и A/B тесты: не упоминался</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>Клиент сформулировал цели.
 Проекты/задачи:
@@ -1609,12 +1418,12 @@
 - Специфика аудитории (синие воротнички с кнопочными телефонами) затрудняет digital-коммуникации | Кто: Директор по маркетингу</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>Директор по маркетингу, Руководитель продукта</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>[Сценарии и триггеры] Нет триггерных коммуникаций — не могут отслеживать, на каком этапе теряется исполнитель, и допушить его
 «у нас сейчас проблема состоит в том, что даже если пользователь-исполнитель начинает процесс регистрации... Он может зависать на каком-то этапе, уходить, и мы, как сервис, не всегда можем это отслеживать»
@@ -1626,24 +1435,183 @@
 «исполнитель при этом либо не заходит в наше приложение, либо забывает про наше приложение, либо он вообще наше приложение не устанавливал, и у него... через веб-версию, через которую, естественно, никакие пуши для него не долетают»</t>
         </is>
       </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2026-06-30T08:21:37Z</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>Попросили отложить</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>Внутренние перестановки, вектор на другое, вернусь позже</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>Коммент при проигрыше: «внутренние перестановки, пока вектор на другое, вернусь позже».</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>364853</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>https://mindbox.pipedrive.com/deal/364853</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>thermex.ru</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Midmarket: SS, так как маленькая база</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>385</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2026-06-02T09:38:57Z</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>Указана причина SS</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>Коммент пуст — по указанной причине/заметкам.</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>364859</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>https://mindbox.pipedrive.com/deal/364859</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Сделка doctor-arbitailo.ru</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Midmarket: не могу получить ответ от клиента</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>449</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2026-06-15T15:02:11Z</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>Клиент перестал отвечать</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>Нет ответа</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>Коммент пуст — по указанной причине/заметкам.</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>364908</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>https://mindbox.pipedrive.com/deal/364908</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ya-apteka.ru</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Midmarket: не могу получить ответ от клиента</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>492</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-06-30T08:21:37Z</t>
+          <t>2026-06-23T11:16:57Z</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>Попросили отложить</t>
+          <t>Клиент перестал отвечать</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>Внутренние перестановки, вектор на другое, вернусь позже</t>
+          <t>Нет ответа</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>Коммент при проигрыше: «внутренние перестановки, пока вектор на другое, вернусь позже».</t>
+          <t>Коммент пуст — по указанной причине/заметкам.</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
@@ -1654,25 +1622,30 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>364823</v>
+        <v>366724</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://mindbox.pipedrive.com/deal/364823</t>
+          <t>https://mindbox.pipedrive.com/deal/366724</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Сделка sk-bauinvest.ru</t>
+          <t>Сделка sibagrotrade.ru</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Персона: Дубль</t>
+          <t>Midmarket: не готовы интегрироваться – напиши почему в Коммент при проигрыше</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>не пускает к лпр, пока не готовы идти в проработку, ценность не выкупила</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>385</v>
+        <v>449</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1681,255 +1654,10 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>CDP / база клиентов: amoCRM | Email: не упоминался | SMS: не упоминался | Мессенджеры: не упоминался | Мобильные пуши / In-app: не упоминался | Чат-боты: не упоминался | Лояльность: не упоминался | Сценарии и триггеры: не упоминался | Персонализация сайта: не упоминался | Квизы и опросы: не упоминался | ML рекомендации: не упоминался | Аналитика и A/B тесты: по базе — не упоминался, по ПЛ — не упоминался, по рекламе — не упоминался, A/B тесты — не упоминался</t>
+          <t>CDP / база клиентов: 1С | Email: Unisender | SMS: не упоминался | Мессенджеры: не упоминался | Мобильные пуши / In-app: не упоминался | Чат-боты: не упоминался | Лояльность: 1С (In-house решение) | Сценарии и триггеры: не упоминался | Персонализация сайта: не упоминался | Квизы и опросы: не упоминался | ML рекомендации: не упоминался | Аналитика и A/B тесты: по базе — не упоминался, по ПЛ — не упоминался, по рекламе — не упоминался, A/B тесты — не упоминался</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
-        <is>
-          <t>Клиент не сформулировал явных целей. Ниже фоновые проблемы и ограничения.
-Проекты/задачи:
-- (основная) Запуск и донастройка нового ЖК (Херсонская область): настройка связок, устранение проблем с CRM | Срок: текущий момент, завершение ориентировочно к началу лета | Кто: маркетолог (предположительно)
-Общие проблемы:
-- Низкий уровень сбора email-адресов от клиентов — многие не оставляют или оставляют с ошибками | Кто: маркетолог (предположительно)
-- amoCRM работает нестабильно («тупит») при запуске нового ЖК | Кто: маркетолог (предположительно)</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>CRM маркетолог</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>[CDP / база клиентов] amoCRM работает с перебоями при запуске нового ЖК
-«еще необходимо там донастроить, доналаживать там связки, связь даже до конца там не совсем, CRM где-то тупит»
-[Общее] Проблемы со сбором email-адресов — клиенты не оставляют или оставляют с ошибками
-«e-mail многие не оставляют, либо частенько ошибаются, непонятно что. Как-то было у нас такое, что мы проводили исследование там внутри, посмотрели, и с e-mail очень много не оставляет кто»</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>2026-06-15T15:21:55Z</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="inlineStr">
-        <is>
-          <t>Нецелевой</t>
-        </is>
-      </c>
-      <c r="Q18" s="3" t="inlineStr">
-        <is>
-          <t>Дубль персоны/сделки</t>
-        </is>
-      </c>
-      <c r="R18" s="3" t="inlineStr">
-        <is>
-          <t>Коммент пуст — по указанной причине/заметкам.</t>
-        </is>
-      </c>
-      <c r="S18" s="3" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>364853</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>https://mindbox.pipedrive.com/deal/364853</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>thermex.ru</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Midmarket: SS, так как маленькая база</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>385</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2026-06-02T09:38:57Z</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="inlineStr">
-        <is>
-          <t>SS</t>
-        </is>
-      </c>
-      <c r="Q19" s="3" t="inlineStr">
-        <is>
-          <t>Указана причина SS</t>
-        </is>
-      </c>
-      <c r="R19" s="3" t="inlineStr">
-        <is>
-          <t>Коммент пуст — по указанной причине/заметкам.</t>
-        </is>
-      </c>
-      <c r="S19" s="3" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>364859</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>https://mindbox.pipedrive.com/deal/364859</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Сделка doctor-arbitailo.ru</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Midmarket: не могу получить ответ от клиента</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>449</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2026-06-15T15:02:11Z</t>
-        </is>
-      </c>
-      <c r="P20" s="3" t="inlineStr">
-        <is>
-          <t>Клиент перестал отвечать</t>
-        </is>
-      </c>
-      <c r="Q20" s="3" t="inlineStr">
-        <is>
-          <t>Нет ответа</t>
-        </is>
-      </c>
-      <c r="R20" s="3" t="inlineStr">
-        <is>
-          <t>Коммент пуст — по указанной причине/заметкам.</t>
-        </is>
-      </c>
-      <c r="S20" s="3" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>364908</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>https://mindbox.pipedrive.com/deal/364908</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>ya-apteka.ru</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Midmarket: не могу получить ответ от клиента</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>492</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2026-06-23T11:16:57Z</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="inlineStr">
-        <is>
-          <t>Клиент перестал отвечать</t>
-        </is>
-      </c>
-      <c r="Q21" s="3" t="inlineStr">
-        <is>
-          <t>Нет ответа</t>
-        </is>
-      </c>
-      <c r="R21" s="3" t="inlineStr">
-        <is>
-          <t>Коммент пуст — по указанной причине/заметкам.</t>
-        </is>
-      </c>
-      <c r="S21" s="3" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>366724</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>https://mindbox.pipedrive.com/deal/366724</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Сделка sibagrotrade.ru</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Midmarket: не готовы интегрироваться – напиши почему в Коммент при проигрыше</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>не пускает к лпр, пока не готовы идти в проработку, ценность не выкупила</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>449</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>CDP / база клиентов: 1С | Email: Unisender | SMS: не упоминался | Мессенджеры: не упоминался | Мобильные пуши / In-app: не упоминался | Чат-боты: не упоминался | Лояльность: 1С (In-house решение) | Сценарии и триггеры: не упоминался | Персонализация сайта: не упоминался | Квизы и опросы: не упоминался | ML рекомендации: не упоминался | Аналитика и A/B тесты: по базе — не упоминался, по ПЛ — не упоминался, по рекламе — не упоминался, A/B тесты — не упоминался</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
         <is>
           <t>Клиент сформулировал цели.
 Метрики:
@@ -1945,12 +1673,12 @@
 - Ограниченный маркетинговый бюджет — стоимость Mindbox 183 000 ₽/мес «как будто бы не впишется» | Кто: маркетолог (предположительно)</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve">, </t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>[Лояльность] Программа лояльности в B2B работает через 1С, функционирует и интегрирована с общей базой
 «для B2B-сегмента у нас действуют программы лояльности. Она как бы есть, она работает. Да, есть. С общей базой.»
@@ -1959,188 +1687,188 @@
 Стоимость: Клиент сказала, что стоимость Mindbox 183 000 ₽/мес «как будто бы это не впишется в наш маркетинговый бюджет». Конкретная стоимость текущего стека не озвучена, но Mindbox воспринимается как слишком дорогой для текущего маркетингового бюджета.</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>[Email] Рассылки только массовые, без персонализации и сегментации — клиент подтвердила интерес к персонализированным рассылкам как к недостающей функциональности
 «скорее это новинки и акции»
 «Вот это было бы актуально больше для розницы»</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>2026-06-15T10:12:30Z</t>
         </is>
       </c>
-      <c r="P22" s="3" t="inlineStr">
+      <c r="P18" s="3" t="inlineStr">
         <is>
           <t>Не заинтересовали ЛВР</t>
         </is>
       </c>
-      <c r="Q22" s="3" t="inlineStr">
+      <c r="Q18" s="3" t="inlineStr">
         <is>
           <t>Ценность не выкупила, не пускает к ЛПР</t>
         </is>
       </c>
-      <c r="R22" s="3" t="inlineStr">
+      <c r="R18" s="3" t="inlineStr">
         <is>
           <t>Коммент при проигрыше: «не пускает к лпр, пока не готовы идти в проработку, ценность не выкупила».</t>
         </is>
       </c>
-      <c r="S22" s="3" t="inlineStr">
+      <c r="S18" s="3" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="n">
+    <row r="19">
+      <c r="A19" t="n">
         <v>367633</v>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>https://mindbox.pipedrive.com/deal/367633</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Сделка shaverma.com</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Midmarket: выбрали конкурента, текущий стек или сделают сами – напиши кому в Коммент при проигрыше</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>айко практически бесплатно для них дало мп и пл</t>
         </is>
       </c>
-      <c r="H23" t="n">
+      <c r="H19" t="n">
         <v>385</v>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
         <is>
           <t>2026-06-04T13:09:20Z</t>
         </is>
       </c>
-      <c r="P23" s="3" t="inlineStr">
+      <c r="P19" s="3" t="inlineStr">
         <is>
           <t>Конкурент</t>
         </is>
       </c>
-      <c r="Q23" s="3" t="inlineStr">
+      <c r="Q19" s="3" t="inlineStr">
         <is>
           <t>iiko (дал маркетплейс и лояльность практически бесплатно)</t>
         </is>
       </c>
-      <c r="R23" s="3" t="inlineStr">
+      <c r="R19" s="3" t="inlineStr">
         <is>
           <t>Коммент при проигрыше: «айко практически бесплатно для них дало мп и пл».</t>
         </is>
       </c>
-      <c r="S23" s="3" t="inlineStr">
+      <c r="S19" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="n">
+    <row r="20">
+      <c r="A20" t="n">
         <v>367876</v>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>https://mindbox.pipedrive.com/deal/367876</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Сделка brunoyam.com</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Midmarket: SS, так как маленькая база</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>передала вика, не оч целевые кмк</t>
         </is>
       </c>
-      <c r="H24" t="n">
+      <c r="H20" t="n">
         <v>449</v>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
         <is>
           <t>2026-06-16T15:55:11Z</t>
         </is>
       </c>
-      <c r="P24" s="3" t="inlineStr">
+      <c r="P20" s="3" t="inlineStr">
         <is>
           <t>SS</t>
         </is>
       </c>
-      <c r="Q24" s="3" t="inlineStr">
+      <c r="Q20" s="3" t="inlineStr">
         <is>
           <t>Указана SS; «не оч целевые»</t>
         </is>
       </c>
-      <c r="R24" s="3" t="inlineStr">
+      <c r="R20" s="3" t="inlineStr">
         <is>
           <t>Коммент при проигрыше: «передала вика, не оч целевые кмк».</t>
         </is>
       </c>
-      <c r="S24" s="3" t="inlineStr">
+      <c r="S20" s="3" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="n">
+    <row r="21">
+      <c r="A21" t="n">
         <v>368136</v>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>https://mindbox.pipedrive.com/deal/368136</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>freedome-realty.ru</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Midmarket до встречи: неприоритетная для меня компания</t>
         </is>
       </c>
-      <c r="H25" t="n">
+      <c r="H21" t="n">
         <v>449</v>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>CDP / база клиентов: Битрикс | Email: Битрикс | SMS: используют, но не определили стек | Мессенджеры: используют, но не определили стек (WhatsApp → переход на МАКС) | Мобильные пуши / In-app: не упоминался | Чат-боты: не упоминался | Лояльность: не упоминался | Сценарии и триггеры: Битрикс | Персонализация сайта: не упоминался | Квизы и опросы: не упоминался | ML рекомендации: не упоминался | Аналитика и A/B тесты: по рекламе — Callibri, по базе — не упоминался, по ПЛ — не упоминался, A/B тесты — нет</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>Клиент не сформулировал явных целей с метриками. Ниже фоновые проблемы и ограничения.
 Проекты/задачи:
@@ -2152,12 +1880,12 @@
 - Мессенджер-рассылки (WhatsApp/SMS/МАКС) работают плохо последние пару месяцев | Кто: маркетолог (предположительно)</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>Маркетолог</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>[Общее] Битрикс закрывает многие этапы работы, клиент работает с ним полноценно
 «у нас просто битрикс, мы битриксом работаем полноценно, и многие этапы он нам закрывает»
@@ -2165,7 +1893,7 @@
 «У нас есть калибри, которая делает подмены номера. Мы можем аналитику смотреть полностью»</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>[Мессенджеры] Рассылки через WhatsApp/SMS/МАКС работают плохо последние пару месяцев, смежная структура
 «у нас был Whatsapp, все подключили. Часть на SMS, часть на Max, но это все работает пока... Нынешние последние пару месяцев не очень хорошо»
@@ -2179,70 +1907,70 @@
 «часть процесса у нас всё равно очень не закрыта»</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>2026-06-11T11:02:58Z</t>
         </is>
       </c>
-      <c r="P25" s="3" t="inlineStr">
-        <is>
-          <t>Клиент перестал отвечать</t>
-        </is>
-      </c>
-      <c r="Q25" s="3" t="inlineStr">
-        <is>
-          <t>Проигрыш до встречи; основатель-ЛПР не вовлёкся</t>
-        </is>
-      </c>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t>Коммент пуст — по указанной причине/заметкам.</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="inlineStr">
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>Не определено</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t>Проигрыш после встречи — реальная причина не ясна, нужна ручная проверка</t>
+        </is>
+      </c>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>Проигран уже после первой встречи; сигналов в комменте/заметках недостаточно для однозначной причины.</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="n">
+    <row r="22">
+      <c r="A22" t="n">
         <v>368735</v>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>https://mindbox.pipedrive.com/deal/368735</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>revyline.ru Назначена встреча</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Midmarket: SS, так как маленькая база</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>собственные каналы продаж пока приносят мало, большие риски что не окупимся</t>
         </is>
       </c>
-      <c r="H26" t="n">
+      <c r="H22" t="n">
         <v>386</v>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>CDP / база клиентов: используют, но не определили стек (разрозненные базы сайта и приложения) | Email: MailGunner (ранее, канал не активен) | SMS: не упоминался | Мессенджеры: не упоминался | Мобильные пуши / In-app: не упоминался (приложение только запущено) | Чат-боты: не интересует | Лояльность: In-house решение (встроена в мобильное приложение) | Сценарии и триггеры: не используют | Персонализация сайта: не упоминался | Квизы и опросы: не упоминался | ML рекомендации: не упоминался | Аналитика и A/B тесты: по базе — не используют, по ПЛ — не упоминался, по рекламе — не упоминался, A/B тесты — нет</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>Клиент сформулировал цели.
 Метрики:
@@ -2264,12 +1992,12 @@
 - Нет аналитики по email-каналу, невозможно оценить эффективность | Кто: маркетолог</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>Маркетолог</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>[Email] Канал полностью неактивен, ранее использовали примитивный инструмент без автоматизации
 «На сегодняшний день мы просто так оживить канал, который мёртв на сегодняшний день вообще»
@@ -2288,128 +2016,128 @@
 «MailGunner самый такой простой, примитивный. Сам напиши, сам отправь, сам построил»</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>2026-06-25T11:25:28Z</t>
         </is>
       </c>
-      <c r="P26" s="3" t="inlineStr">
+      <c r="P22" s="3" t="inlineStr">
         <is>
           <t>SS</t>
         </is>
       </c>
-      <c r="Q26" s="3" t="inlineStr">
+      <c r="Q22" s="3" t="inlineStr">
         <is>
           <t>Указана SS; собственные каналы приносят мало</t>
         </is>
       </c>
-      <c r="R26" s="3" t="inlineStr">
+      <c r="R22" s="3" t="inlineStr">
         <is>
           <t>Коммент при проигрыше: «собственные каналы продаж пока приносят мало, большие риски что не окупимся».</t>
         </is>
       </c>
-      <c r="S26" s="3" t="inlineStr">
+      <c r="S22" s="3" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="n">
+    <row r="23">
+      <c r="A23" t="n">
         <v>368911</v>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>https://mindbox.pipedrive.com/deal/368911</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>speech2text.ru</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Midmarket: выбрали конкурента, текущий стек или сделают сами – напиши кому в Коммент при проигрыше</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>денег нет, не сезон, грею и жду пока вырастут</t>
         </is>
       </c>
-      <c r="H27" t="n">
+      <c r="H23" t="n">
         <v>386</v>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
         <is>
           <t>2026-06-04T13:59:12Z</t>
         </is>
       </c>
-      <c r="P27" s="3" t="inlineStr">
+      <c r="P23" s="3" t="inlineStr">
         <is>
           <t>Попросили отложить</t>
         </is>
       </c>
-      <c r="Q27" s="3" t="inlineStr">
+      <c r="Q23" s="3" t="inlineStr">
         <is>
           <t>Не сезон, грею и жду пока вырастут</t>
         </is>
       </c>
-      <c r="R27" s="3" t="inlineStr">
+      <c r="R23" s="3" t="inlineStr">
         <is>
           <t>Коммент при проигрыше: «денег нет, не сезон, грею и жду пока вырастут».</t>
         </is>
       </c>
-      <c r="S27" s="3" t="inlineStr">
+      <c r="S23" s="3" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="n">
+    <row r="24">
+      <c r="A24" t="n">
         <v>368972</v>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>https://mindbox.pipedrive.com/deal/368972</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Сделка charutti.ru</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Midmarket: SS, так как маленькая база</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>маленькие и текущий инструмент закрывает задачи</t>
         </is>
       </c>
-      <c r="H28" t="n">
+      <c r="H24" t="n">
         <v>385</v>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
         <is>
           <t>CDP / база клиентов: Enkod, Unisender | Email: Enkod, Unisender | SMS: не упоминался | Мессенджеры: используют (Макс), но не определили стек | Мобильные пуши / In-app: не упоминался | Чат-боты: не упоминался | Лояльность: используют, но не определили стек | Сценарии и триггеры: Enkod | Персонализация сайта: используют, но не определили стек | Квизы и опросы: не упоминался | ML рекомендации: In-house решение (ручной подбор) | Аналитика и A/B тесты: по базе — Enkod (RFM), по ПЛ — не упоминался, по рекламе — не упоминался, A/B тесты — не упоминался</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>Клиент не сформулировал явных целей с конкретными метриками. Ниже фоновые проблемы, ограничения и направления развития.
 Проекты/задачи:
@@ -2425,12 +2153,12 @@
 - Неопределённость с мессенджер-каналами (Telegram, Макс) — непонятно, на что делать ставку | Кто: email-маркетолог</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>Email-маркетолог</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>[CDP / база клиентов] Enkod выполняет текущие задачи и доступен по бюджету
 «ENCODE у нас возник как сервис, который выполнял наши задачи на тот момент и в принципе на текущий момент абсолютно также, и как сервис, который нам доступен по оплате»
@@ -2445,7 +2173,7 @@
 Стоимость: Клиент указал, что Mindbox не проходит по бюджету, текущий стек значительно дешевле (конкретные суммы не озвучены). «Мы просто не пролезали по бюджету», «вопрос цены, он очень даже определяющий», «когда мы финансово дорастём до вас, мы обязательно к вам примкнём»</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>[Общее] Текущий стек работает на базовом уровне, есть потенциал для роста
 «на самом деле все довольно на примитивном уровне, то есть на таком базовом хорошем уровне. И конечно у нас с точки зрения потенциала есть много путей для роста»
@@ -2457,9 +2185,241 @@
 «Да, оно очень сыром сейчас, в очень сыром варианте, то есть мы в режиме отлавливания багов и разработки этого всего. Мы не анонсировали нашим клиентам»</t>
         </is>
       </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2026-06-16T16:09:58Z</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t>Указана SS; маленькие + текущий инструмент (Enkod) закрывает</t>
+        </is>
+      </c>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>Коммент при проигрыше: «маленькие и текущий инструмент закрывает задачи».</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>369151</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>https://mindbox.pipedrive.com/deal/369151</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>burvinshop.ru</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Midmarket: не нашел подходящей причины проигрыша – напиши свою в Коммент при проигрыше</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>отложить</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>385</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>2026-06-19T12:15:36Z</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>Попросили отложить</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t>Отложить</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>Коммент при проигрыше: «отложить».</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>369758</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>https://mindbox.pipedrive.com/deal/369758</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>borntobewear.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Midmarket: SS, так как маленькая база</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>нет денег, еле живые</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>385</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2026-06-04T14:21:02Z</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t>Указана SS; «нет денег, еле живые»</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>Коммент при проигрыше: «нет денег, еле живые».</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>370615</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>https://mindbox.pipedrive.com/deal/370615</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>patrickmary.ru</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Midmarket: не готовы интегрироваться – напиши почему в Коммент при проигрыше</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>перенос на 2027</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>386</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2026-06-11T09:19:47Z</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>Попросили отложить</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t>Перенос на 2027</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>Коммент при проигрыше: «перенос на 2027».</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>370832</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>https://mindbox.pipedrive.com/deal/370832</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>legend-tea.ru</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Midmarket до встречи: попросили отложить</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>маленькие и долгие</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>386</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-06-16T16:09:58Z</t>
+          <t>2026-06-24T10:43:48Z</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
@@ -2469,12 +2429,12 @@
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>Указана SS; маленькие + текущий инструмент (Enkod) закрывает</t>
+          <t>Маленькие и долгие</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>Коммент при проигрыше: «маленькие и текущий инструмент закрывает задачи».</t>
+          <t>Коммент при проигрыше: «маленькие и долгие».</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
@@ -2485,274 +2445,42 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>369151</v>
+        <v>370839</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://mindbox.pipedrive.com/deal/369151</t>
+          <t>https://mindbox.pipedrive.com/deal/370839</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>burvinshop.ru</t>
+          <t>Сделка velesmoda.ru</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Midmarket: не нашел подходящей причины проигрыша – напиши свою в Коммент при проигрыше</t>
+          <t>Midmarket: SS, так как маленькая база</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>отложить</t>
+          <t>маленькие, пока отложу</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>385</v>
+        <v>449</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>lost</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>2026-06-19T12:15:36Z</t>
-        </is>
-      </c>
-      <c r="P29" s="3" t="inlineStr">
-        <is>
-          <t>Попросили отложить</t>
-        </is>
-      </c>
-      <c r="Q29" s="3" t="inlineStr">
-        <is>
-          <t>Отложить</t>
-        </is>
-      </c>
-      <c r="R29" s="3" t="inlineStr">
-        <is>
-          <t>Коммент при проигрыше: «отложить».</t>
-        </is>
-      </c>
-      <c r="S29" s="3" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>369758</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>https://mindbox.pipedrive.com/deal/369758</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>borntobewear.com</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Midmarket: SS, так как маленькая база</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>нет денег, еле живые</t>
-        </is>
-      </c>
-      <c r="H30" t="n">
-        <v>385</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>2026-06-04T14:21:02Z</t>
-        </is>
-      </c>
-      <c r="P30" s="3" t="inlineStr">
-        <is>
-          <t>SS</t>
-        </is>
-      </c>
-      <c r="Q30" s="3" t="inlineStr">
-        <is>
-          <t>Указана SS; «нет денег, еле живые»</t>
-        </is>
-      </c>
-      <c r="R30" s="3" t="inlineStr">
-        <is>
-          <t>Коммент при проигрыше: «нет денег, еле живые».</t>
-        </is>
-      </c>
-      <c r="S30" s="3" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>370615</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>https://mindbox.pipedrive.com/deal/370615</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>patrickmary.ru</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Midmarket: не готовы интегрироваться – напиши почему в Коммент при проигрыше</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>перенос на 2027</t>
-        </is>
-      </c>
-      <c r="H31" t="n">
-        <v>386</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>2026-06-11T09:19:47Z</t>
-        </is>
-      </c>
-      <c r="P31" s="3" t="inlineStr">
-        <is>
-          <t>Попросили отложить</t>
-        </is>
-      </c>
-      <c r="Q31" s="3" t="inlineStr">
-        <is>
-          <t>Перенос на 2027</t>
-        </is>
-      </c>
-      <c r="R31" s="3" t="inlineStr">
-        <is>
-          <t>Коммент при проигрыше: «перенос на 2027».</t>
-        </is>
-      </c>
-      <c r="S31" s="3" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>370832</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>https://mindbox.pipedrive.com/deal/370832</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>legend-tea.ru</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Midmarket до встречи: попросили отложить</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>маленькие и долгие</t>
-        </is>
-      </c>
-      <c r="H32" t="n">
-        <v>386</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>2026-06-24T10:43:48Z</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="inlineStr">
-        <is>
-          <t>SS</t>
-        </is>
-      </c>
-      <c r="Q32" s="3" t="inlineStr">
-        <is>
-          <t>Маленькие и долгие</t>
-        </is>
-      </c>
-      <c r="R32" s="3" t="inlineStr">
-        <is>
-          <t>Коммент при проигрыше: «маленькие и долгие».</t>
-        </is>
-      </c>
-      <c r="S32" s="3" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>370839</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>https://mindbox.pipedrive.com/deal/370839</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Сделка velesmoda.ru</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Midmarket: SS, так как маленькая база</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>маленькие, пока отложу</t>
-        </is>
-      </c>
-      <c r="H33" t="n">
-        <v>449</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>CDP / база клиентов: не упоминался | Email: используют, но не определили стек | SMS: не упоминался | Мессенджеры: Flocktory (каскадные уведомления в Telegram, Viber, WhatsApp — клиент говорит, что сейчас не работает) | Мобильные пуши / In-app: не упоминался | Чат-боты: не упоминался | Лояльность: используют, но не определили стек | Сценарии и триггеры: Flocktory | Персонализация сайта: не упоминался | Квизы и опросы: не упоминался | ML рекомендации: не упоминался | Аналитика и A/B тесты: не упоминался</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>Клиент сформулировал цели.
 Метрики:
@@ -2770,19 +2498,19 @@
 - Бюджетные ограничения — опасение, что стоимость Mindbox не окупится | Кто: владелец/руководитель бизнеса (предположительно)</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>Собственник, Разработчик</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>[Email] Текущий инструмент email-рассылок значительно дешевле Mindbox — в 10 раз (конкретные суммы не озвучены)
 «По email рассылкам я как услышал цену… Они в 10 раз выше, чем я сейчас плачу, в 10»
 Стоимость: клиент считает тарифы Mindbox «недетскими», в 10 раз выше текущих расходов на email-рассылки. Конкретные суммы не названы. Клиент опасается, что подключение «уведёт в дикий убыток».</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>[Мессенджеры] Проблемы с доставкой и прочтением сообщений в WhatsApp
 «Сообщение уходит, кто-то прочитал, кто-то не прочитал. Сообщение видим, что доставлено. Сообщение только через три часа прочитано.»
@@ -2800,70 +2528,70 @@
 «все, что бы мы сейчас не подключали на сайте для увеличения конверсии… это только увеличивает расходы, больше ничего»</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>2026-06-16T15:56:44Z</t>
         </is>
       </c>
-      <c r="P33" s="3" t="inlineStr">
+      <c r="P29" s="3" t="inlineStr">
         <is>
           <t>SS</t>
         </is>
       </c>
-      <c r="Q33" s="3" t="inlineStr">
+      <c r="Q29" s="3" t="inlineStr">
         <is>
           <t>Маленькие, пока отложу</t>
         </is>
       </c>
-      <c r="R33" s="3" t="inlineStr">
+      <c r="R29" s="3" t="inlineStr">
         <is>
           <t>Коммент при проигрыше: «маленькие, пока отложу».</t>
         </is>
       </c>
-      <c r="S33" s="3" t="inlineStr">
+      <c r="S29" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="n">
+    <row r="30">
+      <c r="A30" t="n">
         <v>370842</v>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>https://mindbox.pipedrive.com/deal/370842</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Сделка kiber-one.com</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Midmarket: не нашел подходящей причины проигрыша – напиши свою в Коммент при проигрыше</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>франшизы, у каждого свой маркетинг, вообще не связаны между собой, ничем не полезны</t>
         </is>
       </c>
-      <c r="H34" t="n">
+      <c r="H30" t="n">
         <v>385</v>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
         <is>
           <t>CDP / база клиентов: Alpha CRM | Email: используют, но не определили стек | SMS: не интересует | Мессенджеры: не упоминался | Мобильные пуши / In-app: используют, но не определили стек | Чат-боты: не упоминался | Лояльность: не интересует | Сценарии и триггеры: In-house решение | Персонализация сайта: не упоминался | Квизы и опросы: не упоминался | ML рекомендации: не упоминался | Аналитика и A/B тесты: по базе — не упоминался, по ПЛ — не упоминался, по рекламе — не упоминался, A/B тесты — не упоминался</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>Клиент сформулировал цели частично, без количественных метрик.
 Метрики:
@@ -2875,12 +2603,12 @@
 - Малый размер базы головного офиса (3–5 тыс.) и невозможность объединения франшизных баз — структурное ограничение для внедрения платформенных решений | Кто: Маркетолог</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>Маркетолог</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>[Общее] Текущих инструментов достаточно для задач компании
 «Да, достаточно, поэтому мы чаще всего не прибегаем к помощи таких платформ»
@@ -2890,233 +2618,134 @@
 «Если говорить про e-mail, то персонализированные, ситуативные больше по нашим непосредственным сегментам»</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>[Общее] Отсутствие полноценной автоматизации маркетинга, всё делается вручную
 «Всё это у нас разрознено, и мы это делаем вручную, грубо говоря. То есть, какой-то полноценной автоматизации нет»</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>2026-06-28T11:16:25Z</t>
         </is>
       </c>
-      <c r="P34" s="3" t="inlineStr">
+      <c r="P30" s="3" t="inlineStr">
         <is>
           <t>Нецелевой</t>
         </is>
       </c>
-      <c r="Q34" s="3" t="inlineStr">
+      <c r="Q30" s="3" t="inlineStr">
         <is>
           <t>Франшизы, у каждого свой маркетинг, децентрализовано</t>
         </is>
       </c>
-      <c r="R34" s="3" t="inlineStr">
+      <c r="R30" s="3" t="inlineStr">
         <is>
           <t>Коммент при проигрыше: «франшизы, у каждого свой маркетинг, вообще не связаны между собой, ничем не полезны».</t>
         </is>
       </c>
-      <c r="S34" s="3" t="inlineStr">
+      <c r="S30" s="3" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="n">
+    <row r="31">
+      <c r="A31" t="n">
         <v>371048</v>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>https://mindbox.pipedrive.com/deal/371048</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Сделка zn48.ru</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Midmarket: не могу получить ответ от клиента</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>ушёл в игнор, пыталась через коллег его вытащить - никак</t>
         </is>
       </c>
-      <c r="H35" t="n">
+      <c r="H31" t="n">
         <v>449</v>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
         <is>
           <t>2026-06-28T10:55:06Z</t>
         </is>
       </c>
-      <c r="P35" s="3" t="inlineStr">
+      <c r="P31" s="3" t="inlineStr">
         <is>
           <t>Клиент перестал отвечать</t>
         </is>
       </c>
-      <c r="Q35" s="3" t="inlineStr">
+      <c r="Q31" s="3" t="inlineStr">
         <is>
           <t>Ушёл в игнор, через коллег не вытащить</t>
         </is>
       </c>
-      <c r="R35" s="3" t="inlineStr">
+      <c r="R31" s="3" t="inlineStr">
         <is>
           <t>Коммент при проигрыше: «ушёл в игнор, пыталась через коллег его вытащить - никак».</t>
         </is>
       </c>
-      <c r="S35" s="3" t="inlineStr">
+      <c r="S31" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>371562</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>https://mindbox.pipedrive.com/deal/371562</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Сделка rockot-motors.ru</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Персона: Дубль</t>
-        </is>
-      </c>
-      <c r="H36" t="n">
-        <v>385</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>CDP / база клиентов: In-house решение (1С) | Email: Unisender | SMS: не упоминался | Мессенджеры: не упоминался | Мобильные пуши / In-app: не упоминался | Чат-боты: In-house решение (на базе AI, не российский) | Лояльность: In-house решение (1С), только офлайн | Сценарии и триггеры: не упоминался | Персонализация сайта: не упоминался | Квизы и опросы: пробовали, отказались | ML рекомендации: не упоминался | Аналитика и A/B тесты: не упоминался</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Клиент сформулировал цели.
-Проекты/задачи:
-- (основная) Распространить программу лояльности на сайт и объединить онлайн и офлайн ПЛ в единую систему → для возврата клиентов с маркетплейсов и удобства управления | Кто: роль не определена (предположительно, руководитель маркетинга)
-- (второстепенная) Заменить текущий чат-бот на российский сервис без VPN и блокировок | Кто: роль не определена (предположительно, руководитель маркетинга)
-- (второстепенная) Подключить мобильные пуши | Кто: роль не определена (предположительно, руководитель маркетинга)
-Общие проблемы:
-- (основная) Розничный сайт теряет популярность — клиенты уходят на маркетплейсы | Кто: роль не определена (предположительно, руководитель маркетинга)
-- Клиенты смотрят товары на сайте, добавляют в корзину, но покупают на маркетплейсе | Кто: роль не определена (предположительно, руководитель маркетинга)</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>Маркетолог</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>[Email] Unisender полностью устраивает, нет потребности в замене
-«Мы работаем с Unicenter, поэтому в принципе нас все это устраивает. Тут не особо интересно.»
-[CDP / база клиентов] 1С как единая система для всех данных о клиентах, не хотят менять
-«Профили клиента мы встраиваемся все в 1С, у нас комплексная автоматизация, Мы максимально вне работаем, поэтому тоже не пойдем.»
-[Лояльность] Текущая бонусная программа в офлайне работает
-«Она уже действует, она уже работает.»</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>[Чат-боты] Текущий чат-бот работает на нероссийском сервисе, требует VPN, руководство требует уходить от таких решений
-«он работает на базе E, но я хочу что-то переходить более интересное, но мне нужно, чтобы это сервис был российский, то есть чтобы не было никаких ни VPN-ов, ни блоков, ничего, потому что сейчас максимально руководительско от этого уходить»
-[Лояльность] Невозможно распространить ПЛ на сайт из-за сложной архитектуры — сайт самописный и работает через дополнительную программу помимо 1С
-«Мы хотим это внедрить, но у нас сайт работает не только на 1С, он работает еще через другую программу дополнительно, самописный, скажем так, сайт. Вот, поэтому чтобы как раз-таки вот этот движок, внедрить все это, там немножечко сложнее... поэтому на сайте мы пока вот затормаживаемся»
-[Лояльность] ПЛ работает только в офлайне (мотосалоны), нет единой системы для онлайна и офлайна
-«А для мотосалонов, если было бы что-то общее, конечно, намного удобней.»
-[Квизы и опросы] Квизы пробовали, но клиенты их не проходят из-за закрытости аудитории
-«квизы мы проходили, пробовали, но у нас клиенты очень такие закрытые, и мне очень интересно, поэтому они зачастую не проходят их»
-[Общее] Розничный сайт теряет популярность из-за оттока клиентов на маркетплейсы
-«сайт наш розничный, он сейчас стал менее популярен, потому что все пошли на Marketplace»</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>2026-06-15T15:20:16Z</t>
-        </is>
-      </c>
-      <c r="P36" s="3" t="inlineStr">
-        <is>
-          <t>Нецелевой</t>
-        </is>
-      </c>
-      <c r="Q36" s="3" t="inlineStr">
-        <is>
-          <t>Дубль персоны/сделки</t>
-        </is>
-      </c>
-      <c r="R36" s="3" t="inlineStr">
-        <is>
-          <t>Коммент пуст — по указанной причине/заметкам.</t>
-        </is>
-      </c>
-      <c r="S36" s="3" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
+    <row r="32">
+      <c r="A32" t="n">
         <v>371827</v>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>https://mindbox.pipedrive.com/deal/371827</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Сделка mamako.ru</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Midmarket: не готовы интегрироваться – напиши почему в Коммент при проигрыше</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>экономичски проект врядли будет окупаться, но в цифры идти не готовы</t>
         </is>
       </c>
-      <c r="H37" t="n">
+      <c r="H32" t="n">
         <v>449</v>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
         <is>
           <t>CDP / база клиентов: используют, но не определили стек | Email: используют, но не определили стек | SMS: не упоминался | Мессенджеры: не упоминался | Мобильные пуши / In-app: не упоминался | Чат-боты: планируют In-house решение (на базе ИИ) | Лояльность: не упоминался | Сценарии и триггеры: не упоминался | Персонализация сайта: не упоминался | Квизы и опросы: Marquiz | ML рекомендации: не упоминался | Аналитика и A/B тесты: по базе — не упоминался, по ПЛ — не упоминался, по рекламе — нет сквозной аналитики, A/B тесты — не упоминался</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>Клиент сформулировал цели.
 Метрики:
@@ -3134,17 +2763,17 @@
 - Низкая конверсия органического трафика в подписчиков — аудитория приходит за информацией, а не за продуктом | Кто: Руководитель digital-маркетинга</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>Руководитель digital-маркетинга, Руководитель направления</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>Стоимость: Клиент считает тариф Mindbox (150 000 ₽/мес до НДС) экономически необоснованным при текущем размере базы (10 000 подписчиков). Мария: «стоимость общения с клиентом, с учётом стоимости подписки на сервис, получается очень высокой. Соответственно, для того, чтобы снизить, нам нужно увеличить количество клиентов для начала». Конкретная стоимость текущего стека не озвучена.</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>[Email / Сценарии и триггеры] Рассылки делаются вручную, объём ручного труда растёт с масштабом
 «мы ведем рассылки, но чем дальше, тем больше это ручной труд»
@@ -3152,128 +2781,128 @@
 «нет сквозной аналитики у производителей в силу того, что нет возможности посчитать точно источник покупки на маркетплейсах»</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>2026-06-28T11:06:11Z</t>
         </is>
       </c>
-      <c r="P37" s="3" t="inlineStr">
+      <c r="P32" s="3" t="inlineStr">
         <is>
           <t>Клиенту дорого, хотя база норм</t>
         </is>
       </c>
-      <c r="Q37" s="3" t="inlineStr">
+      <c r="Q32" s="3" t="inlineStr">
         <is>
           <t>Проект вряд ли окупается, в цифры идти не готовы</t>
         </is>
       </c>
-      <c r="R37" s="3" t="inlineStr">
+      <c r="R32" s="3" t="inlineStr">
         <is>
           <t>Коммент при проигрыше: «экономичски проект врядли будет окупаться, но в цифры идти не готовы».</t>
         </is>
       </c>
-      <c r="S37" s="3" t="inlineStr">
+      <c r="S32" s="3" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="n">
+    <row r="33">
+      <c r="A33" t="n">
         <v>372106</v>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>https://mindbox.pipedrive.com/deal/372106</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>mymedex.ru Назначена встреча</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Midmarket: не готовы интегрироваться – напиши почему в Коммент при проигрыше</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>отложили проект</t>
         </is>
       </c>
-      <c r="H38" t="n">
+      <c r="H33" t="n">
         <v>386</v>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
         <is>
           <t>2026-06-22T07:32:31Z</t>
         </is>
       </c>
-      <c r="P38" s="3" t="inlineStr">
+      <c r="P33" s="3" t="inlineStr">
         <is>
           <t>Попросили отложить</t>
         </is>
       </c>
-      <c r="Q38" s="3" t="inlineStr">
+      <c r="Q33" s="3" t="inlineStr">
         <is>
           <t>Отложили проект</t>
         </is>
       </c>
-      <c r="R38" s="3" t="inlineStr">
+      <c r="R33" s="3" t="inlineStr">
         <is>
           <t>Коммент при проигрыше: «отложили проект».</t>
         </is>
       </c>
-      <c r="S38" s="3" t="inlineStr">
+      <c r="S33" s="3" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="n">
+    <row r="34">
+      <c r="A34" t="n">
         <v>372343</v>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>https://mindbox.pipedrive.com/deal/372343</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Сделка harrycooper.ru</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Midmarket: выбрали конкурента, текущий стек или сделают сами – напиши кому в Коммент при проигрыше</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>retailcrm, не нашли поводов для перехода</t>
         </is>
       </c>
-      <c r="H39" t="n">
+      <c r="H34" t="n">
         <v>385</v>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
         <is>
           <t>CDP / база клиентов: RetailCRM | Email: используют, но не определили стек | SMS: используют, но не определили стек | Мессенджеры: не используют | Мобильные пуши / In-app: не упоминался | Чат-боты: не упоминался | Лояльность: RetailCRM | Сценарии и триггеры: RetailCRM | Персонализация сайта: не упоминался | Квизы и опросы: не упоминался | ML рекомендации: не упоминался | Аналитика и A/B тесты: по базе — RetailCRM (RFM), по ПЛ — не упоминался, по рекламе — не упоминался, A/B тесты — нет</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>Клиент сформулировал цели.
 Метрики:
@@ -3286,12 +2915,12 @@
 - Точное определение источников трафика и конверсий из рекламных каналов | Кто: Бренд-менеджер</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>Бренд-менеджер</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>[CDP / база клиентов] RetailCRM закрывает сегментацию по категориям и характеристикам товаров
 «В целом Retail CRM все это есть»
@@ -3303,7 +2932,7 @@
 «Да, клиент покупает, ему приходит сертификат на почту»</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>[Общее] Только половина необходимого функционала доступна в текущем стеке
 «Наверное, половина функционала, мне кажется, есть в Retail»
@@ -3311,70 +2940,70 @@
 «Вот только четыре назад сталкивалась с ограничениями, с более точной сегментацией, с определенными возможностями в плане сбора в Stripo»</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>2026-06-02T11:03:37Z</t>
         </is>
       </c>
-      <c r="P39" s="3" t="inlineStr">
+      <c r="P34" s="3" t="inlineStr">
         <is>
           <t>Конкурент</t>
         </is>
       </c>
-      <c r="Q39" s="3" t="inlineStr">
+      <c r="Q34" s="3" t="inlineStr">
         <is>
           <t>RetailCRM (не нашли поводов для перехода)</t>
         </is>
       </c>
-      <c r="R39" s="3" t="inlineStr">
+      <c r="R34" s="3" t="inlineStr">
         <is>
           <t>Коммент при проигрыше: «retailcrm, не нашли поводов для перехода».</t>
         </is>
       </c>
-      <c r="S39" s="3" t="inlineStr">
+      <c r="S34" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="n">
+    <row r="35">
+      <c r="A35" t="n">
         <v>372347</v>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>https://mindbox.pipedrive.com/deal/372347</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Сделка chromolab.ru</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>Midmarket: выбрали конкурента, текущий стек или сделают сами – напиши кому в Коммент при проигрыше</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>сейчас не в приоритете, не продал</t>
         </is>
       </c>
-      <c r="H40" t="n">
+      <c r="H35" t="n">
         <v>492</v>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
         <is>
           <t>CDP / база клиентов: Alphalab, EIP (база врачей) | Email: используют, но не определили стек | SMS: не упоминался | Мессенджеры: используют, но не определили стек | Мобильные пуши / In-app: не упоминался | Чат-боты: используют, но не определили стек | Лояльность: используют, но не определили стек | Сценарии и триггеры: используют, но не определили стек (вручную) | Персонализация сайта: не упоминался | Квизы и опросы: не упоминался | ML рекомендации: не упоминался | Аналитика и A/B тесты: по базе — In-house решение (Alphalab), по ПЛ — не упоминался, по рекламе — не упоминался, A/B тесты — не упоминался</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>Клиент не сформулировал явных целей с метриками. Ниже фоновые проблемы и задачи.
 Проекты/задачи:
@@ -3388,12 +3017,12 @@
 - Бюджетное ограничение — Mindbox (180 000 ₽/мес) оценивается как дорогое решение для текущего масштаба бизнеса (6 городов) | Кто: руководитель отдела маркетинга</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>Руководитель маркетинга, Маркетолог</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>[Общее] Очень низкий процент брошенных корзин — высокая конверсия из заказа на сайте в оплату
 «у нас порядка всего лишь 3-5% брошенных корзин, 15% из них оплачивается на сайте, 85% входит оплату в офисы... я думаю, это такой повод для гордости, да, что там бывает от недели к неделе что 0% брошенных корзин»
@@ -3404,7 +3033,7 @@
 Стоимость: Mindbox 180 000 ₽/мес с НДС — клиент считает это дорогим. Стоимость текущего стека не озвучена. Светлана: «это достаточно дорого для нас, учитывая, что, в принципе, достаточно, ну, как бы многие вещи мы сейчас можем делать уже чуть-чуть, чуть-чуть автоматически. Боюсь, конечно, это такая история классная, дорожская, вообще отличная, но дорогая для нас.»</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>[Аналитика и A/B тесты] Невозможность отследить офлайн-конверсии — клиенты, которые увидели рекламу, но пришли напрямую в офис, не отслеживаются
 «А вот история, что они нас увидели, посмотрели, вышли, а потом, не знаю, зашли на карты, например, построили маршрут и приехали. Вот это мы не можем посмотреть»
@@ -3420,70 +3049,70 @@
 «сейчас многие процессы маркетинга перестраиваются, и мы готовы рассматривать какие-то альтернативные варианты, оптимизации прозрачности и так далее»</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>2026-06-26T10:23:18Z</t>
         </is>
       </c>
-      <c r="P40" s="3" t="inlineStr">
+      <c r="P35" s="3" t="inlineStr">
         <is>
           <t>Клиенту дорого, хотя база норм</t>
         </is>
       </c>
-      <c r="Q40" s="3" t="inlineStr">
+      <c r="Q35" s="3" t="inlineStr">
         <is>
           <t>Серьёзный ценовой барьер (по оценке встречи)</t>
         </is>
       </c>
-      <c r="R40" s="3" t="inlineStr">
+      <c r="R35" s="3" t="inlineStr">
         <is>
           <t>Коммент при проигрыше: «сейчас не в приоритете, не продал».</t>
         </is>
       </c>
-      <c r="S40" s="3" t="inlineStr">
+      <c r="S35" s="3" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="n">
+    <row r="36">
+      <c r="A36" t="n">
         <v>372377</v>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>https://mindbox.pipedrive.com/deal/372377</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>timeweb.com Назначена встреча</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>Midmarket: выбрали конкурента, текущий стек или сделают сами – напиши кому в Коммент при проигрыше</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t xml:space="preserve">выбрали другое решение </t>
         </is>
       </c>
-      <c r="H41" t="n">
+      <c r="H36" t="n">
         <v>449</v>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
         <is>
           <t>CDP / база клиентов: не упоминался | Email: используют, но не определили стек | SMS: не упоминался | Мессенджеры: не упоминался | Мобильные пуши / In-app: не упоминался | Чат-боты: не упоминался | Лояльность: не интересует | Сценарии и триггеры: не упоминался | Персонализация сайта: не упоминался | Квизы и опросы: не упоминался | ML рекомендации: не упоминался | Аналитика и A/B тесты: по базе — не упоминался, по ПЛ — не упоминался, по рекламе — не упоминался, A/B тесты — не упоминался</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>Клиент сформулировал цели.
 Проекты/задачи:
@@ -3496,12 +3125,12 @@
 - (основная) Нет понимания жизненного цикла клиента — не отслеживают, как клиент «живёт» в системе | Кто: руководитель проекта (предположительно)</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>CRM менеджер, Project manager</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>[CDP / база клиентов] Нет понимания жизненного цикла клиента — не отслеживают, как «живёт» клиент
 «Мы хотим понимать, как у нас живет клиент»
@@ -3509,70 +3138,70 @@
 «Мы хотим выстроить нормальные, хорошие цепочки именно писем сейчас»</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>2026-06-15T10:11:36Z</t>
         </is>
       </c>
-      <c r="P41" s="3" t="inlineStr">
+      <c r="P36" s="3" t="inlineStr">
         <is>
           <t>Конкурент</t>
         </is>
       </c>
-      <c r="Q41" s="3" t="inlineStr">
+      <c r="Q36" s="3" t="inlineStr">
         <is>
           <t>Выбрали другое решение (не уточнено)</t>
         </is>
       </c>
-      <c r="R41" s="3" t="inlineStr">
+      <c r="R36" s="3" t="inlineStr">
         <is>
           <t>Коммент при проигрыше: «выбрали другое решение ».</t>
         </is>
       </c>
-      <c r="S41" s="3" t="inlineStr">
+      <c r="S36" s="3" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="n">
+    <row r="37">
+      <c r="A37" t="n">
         <v>372644</v>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>https://mindbox.pipedrive.com/deal/372644</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Сделка getmatch.ru</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>Midmarket: SS, так как маленькая база</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>не супер целевые</t>
         </is>
       </c>
-      <c r="H42" t="n">
+      <c r="H37" t="n">
         <v>385</v>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
         <is>
           <t>CDP / база клиентов: не упоминался | Email: используют, но не определили стек | SMS: не упоминался | Мессенджеры: не упоминался | Мобильные пуши / In-app: не упоминался | Чат-боты: не упоминался | Лояльность: не упоминался | Сценарии и триггеры: используют, но не определили стек | Персонализация сайта: не упоминался | Квизы и опросы: не упоминался | ML рекомендации: не упоминался | Аналитика и A/B тесты: не упоминался</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>Клиент сформулировал цели.
 Метрики:
@@ -3588,12 +3217,12 @@
 - На сайте нет возможности самостоятельной покупки — всё через менеджера | Кто: ответственный за развитие ключевых клиентов и аккаунтинг</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>Руководитель направления, Директор по продажам</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>[Email / Сценарии и триггеры] Уже есть автоматизированные рассылки
 «рассылки мы умеем делать автоматизированные»
@@ -3601,7 +3230,7 @@
 «экспертиза в гипотезах, как поднимать конверсии, нам не нужна»</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>[Общее] Клиенты привлекаются вручную, серьёзная автоматизация отсутствует
 «Мы сейчас, можно сказать, вручную клиентов привлекаем. Здесь нет какой-то такой прям серьезной автоматизации, но мы к этому движемся.»
@@ -3611,128 +3240,128 @@
 «у нас есть внутри текущих клиентов большая аудитория рекрутерская... Мы с ними работаем в ручном режиме.»</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>2026-06-16T15:56:00Z</t>
         </is>
       </c>
-      <c r="P42" s="3" t="inlineStr">
+      <c r="P37" s="3" t="inlineStr">
         <is>
           <t>SS</t>
         </is>
       </c>
-      <c r="Q42" s="3" t="inlineStr">
+      <c r="Q37" s="3" t="inlineStr">
         <is>
           <t>Указана SS; «не супер целевые»</t>
         </is>
       </c>
-      <c r="R42" s="3" t="inlineStr">
+      <c r="R37" s="3" t="inlineStr">
         <is>
           <t>Коммент при проигрыше: «не супер целевые».</t>
         </is>
       </c>
-      <c r="S42" s="3" t="inlineStr">
+      <c r="S37" s="3" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="n">
+    <row r="38">
+      <c r="A38" t="n">
         <v>373382</v>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>https://mindbox.pipedrive.com/deal/373382</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>arnypraht.com</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>Midmarket: выбрали конкурента, текущий стек или сделают сами – напиши кому в Коммент при проигрыше</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>maxma, платят 80к, не готовы менять лояльность</t>
         </is>
       </c>
-      <c r="H43" t="n">
+      <c r="H38" t="n">
         <v>385</v>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
         <is>
           <t>2026-06-01T14:51:21Z</t>
         </is>
       </c>
-      <c r="P43" s="3" t="inlineStr">
+      <c r="P38" s="3" t="inlineStr">
         <is>
           <t>Конкурент</t>
         </is>
       </c>
-      <c r="Q43" s="3" t="inlineStr">
+      <c r="Q38" s="3" t="inlineStr">
         <is>
           <t>Maxma (платят 80к, не готовы менять лояльность)</t>
         </is>
       </c>
-      <c r="R43" s="3" t="inlineStr">
+      <c r="R38" s="3" t="inlineStr">
         <is>
           <t>Коммент при проигрыше: «maxma, платят 80к, не готовы менять лояльность».</t>
         </is>
       </c>
-      <c r="S43" s="3" t="inlineStr">
+      <c r="S38" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="n">
+    <row r="39">
+      <c r="A39" t="n">
         <v>373395</v>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>https://mindbox.pipedrive.com/deal/373395</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Сделка varenichnaya1.ru</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>Midmarket: выбрали конкурента, текущий стек или сделают сами – напиши кому в Коммент при проигрыше</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>с ПБ не готовы слезать + тут интеграция со Смартомато, которой у нас нет</t>
         </is>
       </c>
-      <c r="H44" t="n">
+      <c r="H39" t="n">
         <v>385</v>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
         <is>
           <t>CDP / база клиентов: Премиум бонус | Email: не используют | SMS: используют, но не определили стек | Мессенджеры: не используют | Мобильные пуши / In-app: Smartomato, Премиум бонус | Чат-боты: не упоминался | Лояльность: Премиум бонус | Сценарии и триггеры: Премиум бонус | Персонализация сайта: не упоминался | Квизы и опросы: используют, но не определили стек | ML рекомендации: не упоминался | Аналитика и A/B тесты: по базе — не упоминался, по ПЛ — Премиум бонус, по рекламе — не упоминался, A/B тесты — есть (Премиум бонус)</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>Клиент сформулировал цели.
 Метрики:
@@ -3746,12 +3375,12 @@
 - Отсутствие интеграции Mindbox со Smartomato — потеря канала коммуникации при потенциальном переходе | Кто: руководитель маркетинга (предположительно)</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>Руководитель CRM</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>[Лояльность] Премиум бонус окупается с высоким ROI — от 700 до 900%
 «Окупается у нас, Роме, с учетом всех затрат, варьируется от 700 до 900%»
@@ -3770,7 +3399,7 @@
 Стоимость: Клиент платит за Премиум бонус ~200 000 ₽/мес. Mindbox оценён в 200–250 000 ₽/мес, но клиент указал, что при сопоставимой цене потребуется дополнительная бизнес-единица (CRM-маркетолог) и ресурс на интеграцию, а также отсутствует IT-служба — переход экономически невыгоден: «дополнительную единицу можно выделять только при наличии финансовой выгоды для компании. То есть в любом случае, образно, если life-to-life вы будете по цене одинаковы... При этом нужно будет дать дополнительную единицу. Еще и ресурс на интеграцию. Если что, там отсутствие у нас IT-службы внутренней, это будет прям проблема.»</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>[Email] Полностью отсутствует email-канал коммуникации
 «У нас точно нет коммуникации email, и все с ним связано.»
@@ -3780,70 +3409,70 @@
 «Приложения, они интегрированы. Не уверен, что на сто процентов, потому что смартомат такой своеобразный сервис.»</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>2026-06-02T11:09:07Z</t>
         </is>
       </c>
-      <c r="P44" s="3" t="inlineStr">
+      <c r="P39" s="3" t="inlineStr">
         <is>
           <t>Конкурент</t>
         </is>
       </c>
-      <c r="Q44" s="3" t="inlineStr">
+      <c r="Q39" s="3" t="inlineStr">
         <is>
           <t>Премиум Бонус (не готовы слезать; +нет интеграции со Смартомато)</t>
         </is>
       </c>
-      <c r="R44" s="3" t="inlineStr">
+      <c r="R39" s="3" t="inlineStr">
         <is>
           <t>Коммент при проигрыше: «с ПБ не готовы слезать + тут интеграция со Смартомато, которой у нас нет».</t>
         </is>
       </c>
-      <c r="S44" s="3" t="inlineStr">
+      <c r="S39" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="n">
+    <row r="40">
+      <c r="A40" t="n">
         <v>373588</v>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>https://mindbox.pipedrive.com/deal/373588</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Сделка vivatpizza.ru</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>Midmarket: выбрали конкурента, текущий стек или сделают сами – напиши кому в Коммент при проигрыше</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>crm-функционал закрывает арора, лояльность в рестиках не хотят</t>
         </is>
       </c>
-      <c r="H45" t="n">
+      <c r="H40" t="n">
         <v>385</v>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
         <is>
           <t>CDP / база клиентов: Aurora | Email: не упоминался | SMS: не упоминался | Мессенджеры: не упоминался | Мобильные пуши / In-app: используют, но не определили стек | Чат-боты: не упоминался | Лояльность: Aurora | Сценарии и триггеры: используют, но не определили стек | Персонализация сайта: используют, но не определили стек | Квизы и опросы: не упоминался | ML рекомендации: не упоминался | Аналитика и A/B тесты: по базе — используют, но не определили стек, по ПЛ — не упоминался, по рекламе — не упоминался, A/B тесты — не упоминался</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>Клиент не сформулировал явных целей. Ниже фоновые проблемы и ограничения.
 Проекты/задачи:
@@ -3856,12 +3485,12 @@
 - (второстепенная) Высокие затраты на поддержание оффлайна (персонал, аренда) при соотношении оффлайн/онлайн ~45/55 | Кто: Директор по маркетингу</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>Операционный директор, Директор по маркетингу</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>[Общее] Текущий стек уже покрывает большинство предложенных механик: каскадные рассылки, мотивация на частоту, шкала подарков, промокоды, всплывающие окна
 «По всему остальному, большинство из этого мы и так делаем. То есть у нас и так есть каскадные рассылки, у нас и так есть мотивация и на увеличение чистоты... У нас есть шкала подарков, которая мотивирует увеличить чек... У нас есть несколько разных промокодов на первые заказы. У нас есть постоянные промокоды для постоянников на разные суммы чеков.»
@@ -3871,7 +3500,7 @@
 «Вообще, во-первых, есть такой, есть такая техническая возможность у Aurora и так.»</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>[Лояльность] Программа лояльности не работает в оффлайне — невозможно идентифицировать гостей в зале
 «С гостями в зале я не очень понимаю, честно говоря, как там можно это объединить... зал никак нельзя идентифицировать сейчас»
@@ -3883,70 +3512,70 @@
 «Мы пытались реанимировать эту базу, но там очень все тяжело шло, при том, что это была теплая аудитория, которая постоянно делала заказы ранее.»</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>2026-06-02T11:22:52Z</t>
         </is>
       </c>
-      <c r="P45" s="3" t="inlineStr">
+      <c r="P40" s="3" t="inlineStr">
         <is>
           <t>Конкурент</t>
         </is>
       </c>
-      <c r="Q45" s="3" t="inlineStr">
+      <c r="Q40" s="3" t="inlineStr">
         <is>
           <t>Aurora (CRM-функционал закрывает)</t>
         </is>
       </c>
-      <c r="R45" s="3" t="inlineStr">
+      <c r="R40" s="3" t="inlineStr">
         <is>
           <t>Коммент при проигрыше: «crm-функционал закрывает арора, лояльность в рестиках не хотят».</t>
         </is>
       </c>
-      <c r="S45" s="3" t="inlineStr">
+      <c r="S40" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="n">
+    <row r="41">
+      <c r="A41" t="n">
         <v>375181</v>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>https://mindbox.pipedrive.com/deal/375181</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Сделка kenguru.ru</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>Midmarket: выбрали конкурента, текущий стек или сделают сами – напиши кому в Коммент при проигрыше</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>Не готовы сейчас внедрять</t>
         </is>
       </c>
-      <c r="H46" t="n">
+      <c r="H41" t="n">
         <v>385</v>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
         <is>
           <t>CDP / база клиентов: In-house решение (ERP) | Email: не используют (менее 1% email в базе) | SMS: ранее использовали, сейчас отказались (подорожание) | Мессенджеры: не упоминался | Мобильные пуши / In-app: не упоминался | Чат-боты: не упоминался | Лояльность: In-house решение (ERP, 4 тарифа) | Сценарии и триггеры: In-house решение (ранее активно, сейчас минимально) | Персонализация сайта: не упоминался | Квизы и опросы: не упоминался | ML рекомендации: не упоминался | Аналитика и A/B тесты: по базе — In-house решение (RFM, Excel), по ПЛ — не упоминался, по рекламе — не упоминался, A/B тесты — не упоминался</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>Клиент не сформулировал явных целей. Ниже фоновые проблемы и ограничения.
 Проекты/задачи:
@@ -3958,12 +3587,12 @@
 - Затраты на маркетинговые инициативы воспринимаются как неоправданные при текущей частоте покупок | Кто: Директор по маркетингу</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>Директор по маркетингу</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>[Лояльность] Механика двойных цен стимулирует продажу карт и обеспечивает ~40% использования в магазинах
 «если на ценнике... хорошую цену клиент может получить только при наличии карты. Поэтому мы и продаем неплохо эти карты в магазинах»
@@ -3975,7 +3604,7 @@
 «мы можем выгрузить любые данные клиенте, их сгруппировать. У нас есть Алла-подсчеты, и это все сформировать и работать.»</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>[Лояльность] Бонусный тариф 0.5% неэффективен и вызывает негатив у клиентов
 «На самом деле не работает этот тариф вообще, эти бонусы... клиенты, они воспринимают это даже как оскорбление. Что мне давать вообще 5 рублей, 2 рубля на карте?»
@@ -3993,70 +3622,70 @@
 «Никто это не поддерживает»</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>2026-06-18T16:05:45Z</t>
         </is>
       </c>
-      <c r="P46" s="3" t="inlineStr">
+      <c r="P41" s="3" t="inlineStr">
         <is>
           <t>Клиенту дорого, хотя база норм</t>
         </is>
       </c>
-      <c r="Q46" s="3" t="inlineStr">
+      <c r="Q41" s="3" t="inlineStr">
         <is>
           <t>Нет бюджета на интеграцию, текущий стек «бесплатный»</t>
         </is>
       </c>
-      <c r="R46" s="3" t="inlineStr">
+      <c r="R41" s="3" t="inlineStr">
         <is>
           <t>Коммент при проигрыше: «Не готовы сейчас внедрять».</t>
         </is>
       </c>
-      <c r="S46" s="3" t="inlineStr">
+      <c r="S41" s="3" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="n">
+    <row r="42">
+      <c r="A42" t="n">
         <v>375960</v>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>https://mindbox.pipedrive.com/deal/375960</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>ohtapark.ru Назначена встреча</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>Midmarket: не нашел подходящей причины проигрыша – напиши свою в Коммент при проигрыше</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>хотели за 3 рубля сделать проект по объединению 50+ систем с лояльностью (без прикола) солью, так как не верю  (ушли в закат)</t>
         </is>
       </c>
-      <c r="H47" t="n">
+      <c r="H42" t="n">
         <v>492</v>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
         <is>
           <t>CDP / база клиентов: 1С (несколько баз), Битрикс (планируют) | Email: не упоминался | SMS: не упоминался | Мессенджеры: не упоминался | Мобильные пуши / In-app: не упоминался | Чат-боты: планируют | Лояльность: In-house решение (скидочная система, промокоды), ранее рассматривали Премиум бонус | Сценарии и триггеры: не упоминался | Персонализация сайта: не упоминался | Квизы и опросы: не упоминался | ML рекомендации: не упоминался | Аналитика и A/B тесты: не упоминался</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>Клиент сформулировал цели.
 Проекты/задачи:
@@ -4072,12 +3701,12 @@
 - Разрозненность клиентских баз — базы фитнеса и отеля не связаны между собой | Кто: Технический специалист / интегратор</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>Руководитель проектов, Технический специалист / интегратор</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>[CDP / база клиентов] Разрозненные базы данных, отсутствие единой мастер-базы — базы фитнеса и отеля не связаны между собой
 «У нас сейчас есть порядка трех баз фитнеса и база отеля... между собой базы фактически не общаются»
@@ -4089,128 +3718,128 @@
 «уже три года не могли запустить эту систему лояльности с другими платформами, потому что мы потыкались как раз на механике именно интеграции наших систем»</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>2026-06-23T08:06:37Z</t>
         </is>
       </c>
-      <c r="P47" s="3" t="inlineStr">
+      <c r="P42" s="3" t="inlineStr">
         <is>
           <t>Клиенту дорого, хотя база норм</t>
         </is>
       </c>
-      <c r="Q47" s="3" t="inlineStr">
+      <c r="Q42" s="3" t="inlineStr">
         <is>
           <t>Хотели объединить 50+ систем «за 3 рубля» — нереалистичный бюджет</t>
         </is>
       </c>
-      <c r="R47" s="3" t="inlineStr">
+      <c r="R42" s="3" t="inlineStr">
         <is>
           <t>Коммент при проигрыше: «хотели за 3 рубля сделать проект по объединению 50+ систем с лояльностью (без прикола) солью, так как не верю  (ушли в закат)».</t>
         </is>
       </c>
-      <c r="S47" s="3" t="inlineStr">
+      <c r="S42" s="3" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="n">
+    <row r="43">
+      <c r="A43" t="n">
         <v>376785</v>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>https://mindbox.pipedrive.com/deal/376785</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>белая-техника.рф</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>Midmarket: выбрали конкурента, текущий стек или сделают сами – напиши кому в Коммент при проигрыше</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>тугой лпр, мечутся между самописом и готовым решением, денег жалко очень</t>
         </is>
       </c>
-      <c r="H48" t="n">
+      <c r="H43" t="n">
         <v>386</v>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
         <is>
           <t>2026-06-04T13:49:28Z</t>
         </is>
       </c>
-      <c r="P48" s="3" t="inlineStr">
+      <c r="P43" s="3" t="inlineStr">
         <is>
           <t>Руководитель заблокировал решение</t>
         </is>
       </c>
-      <c r="Q48" s="3" t="inlineStr">
+      <c r="Q43" s="3" t="inlineStr">
         <is>
           <t>Тугой ЛПР, денег жалко; мечется между самописом и готовым</t>
         </is>
       </c>
-      <c r="R48" s="3" t="inlineStr">
+      <c r="R43" s="3" t="inlineStr">
         <is>
           <t>Коммент при проигрыше: «тугой лпр, мечутся между самописом и готовым решением, денег жалко очень».</t>
         </is>
       </c>
-      <c r="S48" s="3" t="inlineStr">
+      <c r="S43" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="n">
+    <row r="44">
+      <c r="A44" t="n">
         <v>377542</v>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>https://mindbox.pipedrive.com/deal/377542</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>frankmeat.ru</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>Midmarket: выбрали конкурента, текущий стек или сделают сами – напиши кому в Коммент при проигрыше</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>на ремаркеде, не готовы менять платформу</t>
         </is>
       </c>
-      <c r="H49" t="n">
+      <c r="H44" t="n">
         <v>385</v>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
         <is>
           <t>CDP / база клиентов: Remarket | Email: не используют | SMS: не используют | Мессенджеры: не упоминался | Мобильные пуши / In-app: Remarket | Чат-боты: не упоминался | Лояльность: Remarket | Сценарии и триггеры: Remarket (базовые) | Персонализация сайта: не упоминался | Квизы и опросы: не упоминался | ML рекомендации: не упоминался | Аналитика и A/B тесты: по базе — не упоминался, по ПЛ — не упоминался, по рекламе — не упоминался, A/B тесты — не упоминался</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>Клиент сформулировал цели.
 Проекты/задачи:
@@ -4222,12 +3851,12 @@
 - Переход на другого подрядчика (с Remarket) воспринимается как компромисс — увеличение сложности стека и стоимости обслуживания | Кто: предположительно директор по развитию</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>Директор по развитию</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>[Общее] Remarket закрывает все потребности клиента, переход на другого подрядчика воспринимается как компромисс
 «ремаркет как раз закрывает все наши потребности... переход к каким-то другим подрядчикам для нас компромиссное решение»
@@ -4239,7 +3868,7 @@
 «несколько подрядчиков это более сложный стэк и более дорогое обслуживание»</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>[Сценарии и триггеры] Remarket предположительно не поддерживает отслеживание брошенных корзин и триггерные пуши
 «такие события, как брошенная корзина, я вообще не уверен, что у них можно отслеживать и давать какие-то там триггерные пуши пользователю»
@@ -4247,70 +3876,70 @@
 «Мы пока сейчас работаем на базовых каких-то механиках, потому что все равно достаточное количество проблем пока что существует, которые в первую очередь необходимо решить, а потом уже усложнять коммуникацию»</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>2026-06-18T15:42:22Z</t>
         </is>
       </c>
-      <c r="P49" s="3" t="inlineStr">
+      <c r="P44" s="3" t="inlineStr">
         <is>
           <t>Конкурент</t>
         </is>
       </c>
-      <c r="Q49" s="3" t="inlineStr">
+      <c r="Q44" s="3" t="inlineStr">
         <is>
           <t>Remarked (не готовы менять платформу)</t>
         </is>
       </c>
-      <c r="R49" s="3" t="inlineStr">
+      <c r="R44" s="3" t="inlineStr">
         <is>
           <t>Коммент при проигрыше: «на ремаркеде, не готовы менять платформу».</t>
         </is>
       </c>
-      <c r="S49" s="3" t="inlineStr">
+      <c r="S44" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="n">
+    <row r="45">
+      <c r="A45" t="n">
         <v>377744</v>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>https://mindbox.pipedrive.com/deal/377744</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>barparka.ru</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>Midmarket: не готовы интегрироваться – напиши почему в Коммент при проигрыше</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>запускатьс готовы только на 2 бара, на весь холдинг нет, поэтому вернемся к диалогу позже, будем поддерживать контакт</t>
         </is>
       </c>
-      <c r="H50" t="n">
+      <c r="H45" t="n">
         <v>385</v>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
         <is>
           <t>CDP / база клиентов: Remarket | Email: не используют | SMS: не упоминался | Мессенджеры: Remarket (Telegram-бот) | Мобильные пуши / In-app: не используют (нет приложения) | Чат-боты: Remarket (самописный бот) | Лояльность: Remarket | Сценарии и триггеры: Remarket | Персонализация сайта: не упоминался | Квизы и опросы: Remarket | ML рекомендации: не упоминался | Аналитика и A/B тесты: по базе — Remarket, по ПЛ — Remarket, по рекламе — не упоминался, A/B тесты — нет</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>Клиент не сформулировал явных целей. Ниже фоновые проблемы и ограничения.
 Проекты/задачи:
@@ -4324,12 +3953,12 @@
 - Дисбаланс в программе лояльности — списания превышают начисления | Кто: CRM менеджер</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>Руководитель направления, CRM менеджер</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>[Общее] Система регулярно падает
 «есть как бы моменты, которые не устраивают существование того, что у них без конца что-то слетает»
@@ -4351,70 +3980,70 @@
 «у нас в ремаркете сейчас падают списания больше, чем начисления»</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>2026-06-28T10:47:59Z</t>
         </is>
       </c>
-      <c r="P50" s="3" t="inlineStr">
+      <c r="P45" s="3" t="inlineStr">
         <is>
           <t>Попросили отложить</t>
         </is>
       </c>
-      <c r="Q50" s="3" t="inlineStr">
+      <c r="Q45" s="3" t="inlineStr">
         <is>
           <t>Готовы только на 2 бара, на холдинг нет — вернёмся</t>
         </is>
       </c>
-      <c r="R50" s="3" t="inlineStr">
+      <c r="R45" s="3" t="inlineStr">
         <is>
           <t>Коммент при проигрыше: «запускатьс готовы только на 2 бара, на весь холдинг нет, поэтому вернемся к диалогу позже, будем поддерживать контакт».</t>
         </is>
       </c>
-      <c r="S50" s="3" t="inlineStr">
+      <c r="S45" s="3" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="n">
+    <row r="46">
+      <c r="A46" t="n">
         <v>377951</v>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>https://mindbox.pipedrive.com/deal/377951</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Сделка labspacefit.ru</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>Midmarket: выбрали конкурента, текущий стек или сделают сами – напиши кому в Коммент при проигрыше</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>Mobifitness(закрытая API)</t>
         </is>
       </c>
-      <c r="H51" t="n">
+      <c r="H46" t="n">
         <v>385</v>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
         <is>
           <t>CDP / база клиентов: MobiFitness (CRM), AMA | Email: Unisender | SMS: МТС Маркетолог | Мессенджеры: не упоминался | Мобильные пуши / In-app: не упоминался | Чат-боты: используют, но не определили стек | Лояльность: MobiFitness (встроенная) | Сценарии и триггеры: MobiFitness (встроенная) | Персонализация сайта: не упоминался | Квизы и опросы: не упоминался | ML рекомендации: не упоминался | Аналитика и A/B тесты: по базе — AMA (частично), по ПЛ — не упоминался, по рекламе — не упоминался, A/B тесты — не упоминался</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>Клиент не сформулировал явных целей. Ниже фоновые проблемы и ограничения.
 Общие проблемы:
@@ -4425,12 +4054,12 @@
 - Ручная сегментация базы для SMS-рассылок — трудоёмкий процесс без автоматизации | Кто: Руководитель маркетинга</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>Руководитель маркетинга</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>[CDP / база клиентов] CRM закрыта, нет API — данные можно получить только ручной выгрузкой в CSV
 «у нас CRM-ка наша, она закрыта MAPI, вот, и единственное, что тут можно вытаскивать, это вручную выгрузки там в CSVшках»
@@ -4446,186 +4075,186 @@
 «Ну вот я пока на это все смотрю, и как будто оно все рушится пока что.»</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>2026-06-01T11:45:51Z</t>
         </is>
       </c>
-      <c r="P51" s="3" t="inlineStr">
+      <c r="P46" s="3" t="inlineStr">
         <is>
           <t>Интеграция</t>
         </is>
       </c>
-      <c r="Q51" s="3" t="inlineStr">
+      <c r="Q46" s="3" t="inlineStr">
         <is>
           <t>Нет интеграции с MobiFitness (закрытый API)</t>
         </is>
       </c>
-      <c r="R51" s="3" t="inlineStr">
+      <c r="R46" s="3" t="inlineStr">
         <is>
           <t>Коммент при проигрыше: «Mobifitness(закрытая API)».</t>
         </is>
       </c>
-      <c r="S51" s="3" t="inlineStr">
+      <c r="S46" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="n">
+    <row r="47">
+      <c r="A47" t="n">
         <v>378784</v>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>https://mindbox.pipedrive.com/deal/378784</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>smpracing.ru</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>Midmarket: SS, так как маленькая база</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>зачатачное состояние маркетинга, если продажа то через пол года не раньше</t>
         </is>
       </c>
-      <c r="H52" t="n">
+      <c r="H47" t="n">
         <v>385</v>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
         <is>
           <t>2026-06-04T14:20:29Z</t>
         </is>
       </c>
-      <c r="P52" s="3" t="inlineStr">
+      <c r="P47" s="3" t="inlineStr">
         <is>
           <t>SS</t>
         </is>
       </c>
-      <c r="Q52" s="3" t="inlineStr">
+      <c r="Q47" s="3" t="inlineStr">
         <is>
           <t>Указана SS; зачаточный маркетинг</t>
         </is>
       </c>
-      <c r="R52" s="3" t="inlineStr">
+      <c r="R47" s="3" t="inlineStr">
         <is>
           <t>Коммент при проигрыше: «зачатачное состояние маркетинга, если продажа то через пол года не раньше».</t>
         </is>
       </c>
-      <c r="S52" s="3" t="inlineStr">
+      <c r="S47" s="3" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="n">
+    <row r="48">
+      <c r="A48" t="n">
         <v>379056</v>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>https://mindbox.pipedrive.com/deal/379056</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Сделка sedelice.ru</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>Midmarket: выбрали конкурента, текущий стек или сделают сами – напиши кому в Коммент при проигрыше</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>сидят на том же инструменте - outsource.store</t>
         </is>
       </c>
-      <c r="H53" t="n">
+      <c r="H48" t="n">
         <v>385</v>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
         <is>
           <t>2026-06-18T16:47:57Z</t>
         </is>
       </c>
-      <c r="P53" s="3" t="inlineStr">
+      <c r="P48" s="3" t="inlineStr">
         <is>
           <t>Конкурент</t>
         </is>
       </c>
-      <c r="Q53" s="3" t="inlineStr">
+      <c r="Q48" s="3" t="inlineStr">
         <is>
           <t>Остались на outsource.store</t>
         </is>
       </c>
-      <c r="R53" s="3" t="inlineStr">
+      <c r="R48" s="3" t="inlineStr">
         <is>
           <t>Коммент при проигрыше: «сидят на том же инструменте - outsource.store».</t>
         </is>
       </c>
-      <c r="S53" s="3" t="inlineStr">
+      <c r="S48" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="n">
+    <row r="49">
+      <c r="A49" t="n">
         <v>379135</v>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>https://mindbox.pipedrive.com/deal/379135</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>bestwine24.ru</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>Midmarket: выбрали конкурента, текущий стек или сделают сами – напиши кому в Коммент при проигрыше</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>не окупаются у нас даже на 120 с ндс</t>
         </is>
       </c>
-      <c r="H54" t="n">
+      <c r="H49" t="n">
         <v>385</v>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
         <is>
           <t>CDP / база клиентов: In-house решение | Email: используют, но не определили стек | SMS: не упоминался | Мессенджеры: не упоминался | Мобильные пуши / In-app: не упоминался | Чат-боты: не упоминался | Лояльность: используют, но не определили стек | Сценарии и триггеры: In-house решение | Персонализация сайта: используют, но не определили стек | Квизы и опросы: не упоминался | ML рекомендации: In-house решение | Аналитика и A/B тесты: по базе — In-house решение, по ПЛ — не упоминался, по рекламе — не упоминался, A/B тесты — нет</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>Клиент сформулировал цели.
 Метрики:
@@ -4635,12 +4264,12 @@
 - (основная) Недостаточный уровень продаж — «у меня болят продажи, это самое главное» | Кто: Собственник (предположительно)</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>Собственник</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>[Общее] Клиент считает, что может повторить функционал Mindbox собственными силами на своём объёме
 «получается, что сейчас фактически я могу повторить то, что вы делаете на своем объеме»
@@ -4654,7 +4283,7 @@
 «это слишком большая сумма для нас в месяц... трат с вероятностью 100 процентов и преимущество с вероятностью ну какой-то»</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>[CDP / база клиентов] Не могут отслеживать поведение клиентов на сайте (просмотры карточек, куки)
 «мы, может быть, не отслеживаем, сколько раз он перешел на карточку какую-нибудь. По кукам. То есть нам сложно.»
@@ -4664,70 +4293,70 @@
 «у меня примерно 13 процентов они возвращаются в течение 60 дней, а мне нужно например таких 26 или в два раза больше»</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>2026-06-08T04:10:00Z</t>
         </is>
       </c>
-      <c r="P54" s="3" t="inlineStr">
+      <c r="P49" s="3" t="inlineStr">
         <is>
           <t>Клиенту дорого, хотя база норм</t>
         </is>
       </c>
-      <c r="Q54" s="3" t="inlineStr">
+      <c r="Q49" s="3" t="inlineStr">
         <is>
           <t>«Не окупаемся даже на 120 с НДС»</t>
         </is>
       </c>
-      <c r="R54" s="3" t="inlineStr">
+      <c r="R49" s="3" t="inlineStr">
         <is>
           <t>Коммент при проигрыше: «не окупаются у нас даже на 120 с ндс».</t>
         </is>
       </c>
-      <c r="S54" s="3" t="inlineStr">
+      <c r="S49" s="3" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="n">
+    <row r="50">
+      <c r="A50" t="n">
         <v>379199</v>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>https://mindbox.pipedrive.com/deal/379199</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>glenfield.ru Назначена встреча</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>Midmarket: выбрали конкурента, текущий стек или сделают сами – напиши кому в Коммент при проигрыше</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>loymax - не готовы переезжать еще долго + кассы на каком-то древнем говне</t>
         </is>
       </c>
-      <c r="H55" t="n">
+      <c r="H50" t="n">
         <v>385</v>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
         <is>
           <t>CDP / база клиентов: Loymax | Email: не упоминался | SMS: используют, но не определили стек | Мессенджеры: планируют | Мобильные пуши / In-app: не упоминался | Чат-боты: планируют | Лояльность: Loymax | Сценарии и триггеры: не упоминался | Персонализация сайта: не упоминался | Квизы и опросы: не упоминался | ML рекомендации: Рассматривает: Loimax AI | Аналитика и A/B тесты: по базе — не упоминался, по ПЛ — не упоминался, по рекламе — не упоминался, A/B тесты — не упоминался</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>Клиент сформулировал цели.
 Проекты/задачи:
@@ -4740,12 +4369,12 @@
 - Внутреннее сопротивление изменениям: сотрудники привыкли к старой системе и не хотят менять | Кто: Руководитель программ лояльности</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>Руководитель программ лояльности</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>[Лояльность] Loymax покрывает подавляющее большинство потребностей компании, клиент удовлетворён функциональностью
 «на 95 процентов Лоймэк нас вполне устраивает»
@@ -4755,7 +4384,7 @@
 «все, что нам удалось подключить, нас, как я говорю, на 95% устраивает. То есть, в принципе, что хотели, то получили»</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>[ML рекомендации] Loimax AI пока не решает задачу таргетирования рассылок
 «это отдельный функционал, я тоже его возможности анализирую, пока по всему не все так радужно, то есть вот прямо взять и решить эту задачу пока не можем»
@@ -4765,176 +4394,176 @@
 «Кассы у нас на самописной кассовой программе, она самописная учетная программа, поэтому все эти проблемы с интеграцией»</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>2026-06-02T11:40:37Z</t>
         </is>
       </c>
-      <c r="P55" s="3" t="inlineStr">
+      <c r="P50" s="3" t="inlineStr">
         <is>
           <t>Конкурент</t>
         </is>
       </c>
-      <c r="Q55" s="3" t="inlineStr">
+      <c r="Q50" s="3" t="inlineStr">
         <is>
           <t>Loymax (не готовы переезжать; кассы на старом ПО)</t>
         </is>
       </c>
-      <c r="R55" s="3" t="inlineStr">
+      <c r="R50" s="3" t="inlineStr">
         <is>
           <t>Коммент при проигрыше: «loymax - не готовы переезжать еще долго + кассы на каком-то древнем говне».</t>
         </is>
       </c>
-      <c r="S55" s="3" t="inlineStr">
+      <c r="S50" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="n">
+    <row r="51">
+      <c r="A51" t="n">
         <v>379597</v>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>https://mindbox.pipedrive.com/deal/379597</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Сделка silvercinema.ru</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>Midmarket: не готовы интегрироваться – напиши почему в Коммент при проигрыше</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>Партнер использует Киноплан для бронирования билетов, со слов сотрудников Киноплана, там нет открытого API, что не дает нам возможности интегрироваться</t>
         </is>
       </c>
-      <c r="H56" t="n">
+      <c r="H51" t="n">
         <v>385</v>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
         <is>
           <t>2026-06-08T11:47:28Z</t>
         </is>
       </c>
-      <c r="P56" s="3" t="inlineStr">
+      <c r="P51" s="3" t="inlineStr">
         <is>
           <t>Интеграция</t>
         </is>
       </c>
-      <c r="Q56" s="3" t="inlineStr">
+      <c r="Q51" s="3" t="inlineStr">
         <is>
           <t>Нет интеграции с Киноплан (бронирование билетов)</t>
         </is>
       </c>
-      <c r="R56" s="3" t="inlineStr">
+      <c r="R51" s="3" t="inlineStr">
         <is>
           <t>Коммент при проигрыше: «Партнер использует Киноплан для бронирования билетов, со слов сотрудников Киноплана, там нет открытого API, что не дает нам возможности интегрироваться».</t>
         </is>
       </c>
-      <c r="S56" s="3" t="inlineStr">
+      <c r="S51" s="3" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="n">
+    <row r="52">
+      <c r="A52" t="n">
         <v>379830</v>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>https://mindbox.pipedrive.com/deal/379830</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>kometa.fit</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>Нам отказали: выбрали конкурентов или решили делать сами</t>
         </is>
       </c>
-      <c r="H57" t="n">
+      <c r="H52" t="n">
         <v>492</v>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
         <is>
           <t>2026-06-24T11:55:51Z</t>
         </is>
       </c>
-      <c r="P57" s="3" t="inlineStr">
+      <c r="P52" s="3" t="inlineStr">
         <is>
           <t>Конкурент</t>
         </is>
       </c>
-      <c r="Q57" s="3" t="inlineStr">
+      <c r="Q52" s="3" t="inlineStr">
         <is>
           <t>Решили делать сами (АМО + переход на самописную CRM), управляет РОП</t>
         </is>
       </c>
-      <c r="R57" s="3" t="inlineStr">
+      <c r="R52" s="3" t="inlineStr">
         <is>
           <t>Коммент пуст — по указанной причине/заметкам.</t>
         </is>
       </c>
-      <c r="S57" s="3" t="inlineStr">
+      <c r="S52" s="3" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="n">
+    <row r="53">
+      <c r="A53" t="n">
         <v>380409</v>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>https://mindbox.pipedrive.com/deal/380409</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>максимед-орто.рф Назначена встреча</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>Мы отказали: уровень не соответствует Сильвер+</t>
         </is>
       </c>
-      <c r="H58" t="n">
+      <c r="H53" t="n">
         <v>449</v>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
         <is>
           <t>CDP / база клиентов: 1С (УТ11) | Email: не упоминался | SMS: используют, но не определили стек | Мессенджеры: не упоминался | Мобильные пуши / In-app: не упоминался | Чат-боты: Maxma | Лояльность: 1С (УТ11, встроенная) | Сценарии и триггеры: не упоминался | Персонализация сайта: не упоминался | Квизы и опросы: не упоминался | ML рекомендации: не упоминался | Аналитика и A/B тесты: по базе — не упоминался, по ПЛ — не упоминался, по рекламе — не упоминался, A/B тесты — нет</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>Клиент сформулировал цели.
 Проекты/задачи:
@@ -4945,12 +4574,12 @@
 - (второстепенная) Сайт работает не в полной мере, даёт ~1 заказ в неделю | Кто: Собственник</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>Собственник, Руководитель IT</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>[Лояльность] Бонусная система в 1С (УТ11) несовершенна, требует доработки
 «У нас УТ11, мы на нее не так давно перешли. Она очень несовершенна... нам нужно эти бонусные баллы улучшить с ними работу.»
@@ -4962,123 +4591,123 @@
 «Наш сайт еще работает не в полной мере... какие-то заказы через сайт сейчас поступают. Это может быть раз в недельку.»</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>2026-06-24T13:44:58Z</t>
         </is>
       </c>
-      <c r="P58" s="3" t="inlineStr">
+      <c r="P53" s="3" t="inlineStr">
         <is>
           <t>Нецелевой</t>
         </is>
       </c>
-      <c r="Q58" s="3" t="inlineStr">
+      <c r="Q53" s="3" t="inlineStr">
         <is>
           <t>Мы отказали — уровень не подходит</t>
         </is>
       </c>
-      <c r="R58" s="3" t="inlineStr">
+      <c r="R53" s="3" t="inlineStr">
         <is>
           <t>Коммент пуст — по указанной причине/заметкам.</t>
         </is>
       </c>
-      <c r="S58" s="3" t="inlineStr">
+      <c r="S53" s="3" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="n">
+    <row r="54">
+      <c r="A54" t="n">
         <v>381177</v>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>https://mindbox.pipedrive.com/deal/381177</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>Сделка progressdk.ru</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>Midmarket: выбрали конкурента, текущий стек или сделают сами – напиши кому в Коммент при проигрыше</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>не целевые</t>
         </is>
       </c>
-      <c r="H59" t="n">
+      <c r="H54" t="n">
         <v>385</v>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
         <is>
           <t>2026-06-16T13:22:23Z</t>
         </is>
       </c>
-      <c r="P59" s="3" t="inlineStr">
+      <c r="P54" s="3" t="inlineStr">
         <is>
           <t>Нецелевой</t>
         </is>
       </c>
-      <c r="Q59" s="3" t="inlineStr">
+      <c r="Q54" s="3" t="inlineStr">
         <is>
           <t>Не целевые</t>
         </is>
       </c>
-      <c r="R59" s="3" t="inlineStr">
+      <c r="R54" s="3" t="inlineStr">
         <is>
           <t>Коммент при проигрыше: «не целевые».</t>
         </is>
       </c>
-      <c r="S59" s="3" t="inlineStr">
+      <c r="S54" s="3" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="n">
+    <row r="55">
+      <c r="A55" t="n">
         <v>383905</v>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>https://mindbox.pipedrive.com/deal/383905</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>exactfarming.com</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>MDR: SS (маленькая база, не окупится)</t>
         </is>
       </c>
-      <c r="H60" t="n">
+      <c r="H55" t="n">
         <v>385</v>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
         <is>
           <t>CDP / база клиентов: Dasha Mail, AmaCRM | Email: Dasha Mail | SMS: SMS-таргет | Мессенджеры: Vazap | Мобильные пуши / In-app: не упоминался | Чат-боты: не упоминался | Лояльность: не упоминался | Сценарии и триггеры: планируют | Персонализация сайта: Tilda | Квизы и опросы: Tilda (в процессе настройки) | ML рекомендации: не упоминался | Аналитика и A/B тесты: по базе — не упоминался, по ПЛ — не упоминался, по рекламе — не упоминался, A/B тесты — нет</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>Клиент сформулировал цели.
 Проекты/задачи:
@@ -5097,12 +4726,12 @@
 - Возрастная аудитория плохо реагирует на ботов в мессенджерах, нужны прямые сообщения | Кто: Маркетолог</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>Маркетолог</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>[CDP / база клиентов] Ручная сегментация: данные из разных систем приходится схлопывать вручную
 «вся база клиентов, она через Tilda уходит в нашу платформу для рассылок с помощью интеграции и также в AmaSeren, откуда также в дальнейшем я тоже выгружаю» (подтвердила ручное схлопывание: «Да»)
@@ -5112,118 +4741,118 @@
 «немного не дошла до того, чтобы реализовать момент с тем, как передавать в итоге данные»</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>2026-06-24T06:35:02Z</t>
         </is>
       </c>
-      <c r="P60" s="3" t="inlineStr">
+      <c r="P55" s="3" t="inlineStr">
         <is>
           <t>SS</t>
         </is>
       </c>
-      <c r="Q60" s="3" t="inlineStr">
+      <c r="Q55" s="3" t="inlineStr">
         <is>
           <t>Указана причина SS</t>
         </is>
       </c>
-      <c r="R60" s="3" t="inlineStr">
+      <c r="R55" s="3" t="inlineStr">
         <is>
           <t>Коммент пуст — по указанной причине/заметкам.</t>
         </is>
       </c>
-      <c r="S60" s="3" t="inlineStr">
+      <c r="S55" s="3" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="n">
+    <row r="56">
+      <c r="A56" t="n">
         <v>383977</v>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>https://mindbox.pipedrive.com/deal/383977</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>flik-flyak.ru</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>Midmarket: не нашел подходящей причины проигрыша – напиши свою в Коммент при проигрыше</t>
         </is>
       </c>
-      <c r="H61" t="n">
+      <c r="H56" t="n">
         <v>385</v>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
         <is>
           <t>2026-06-19T13:40:56Z</t>
         </is>
       </c>
-      <c r="P61" s="3" t="inlineStr">
+      <c r="P56" s="3" t="inlineStr">
         <is>
           <t>Клиенту дорого, хотя база норм</t>
         </is>
       </c>
-      <c r="Q61" s="3" t="inlineStr">
+      <c r="Q56" s="3" t="inlineStr">
         <is>
           <t>Маленький (3-5 млн/мес), не потянут 150к</t>
         </is>
       </c>
-      <c r="R61" s="3" t="inlineStr">
+      <c r="R56" s="3" t="inlineStr">
         <is>
           <t>Коммент пуст — по указанной причине/заметкам.</t>
         </is>
       </c>
-      <c r="S61" s="3" t="inlineStr">
+      <c r="S56" s="3" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="n">
+    <row r="57">
+      <c r="A57" t="n">
         <v>383987</v>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>https://mindbox.pipedrive.com/deal/383987</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>tichpizza.ru Назначена встреча</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>Midmarket: SS, так как маленькая база</t>
         </is>
       </c>
-      <c r="H62" t="n">
+      <c r="H57" t="n">
         <v>385</v>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
         <is>
           <t>CDP / база клиентов: In-house решение (в разработке) | Email: используют, но не определили стек | SMS: МегаСМС | Мессенджеры: используют, но не определили стек (ВК рассылки) | Мобильные пуши / In-app: используют, но не определили стек | Чат-боты: планируют | Лояльность: Гулеш (встроенная) | Сценарии и триггеры: In-house решение (в разработке) | Персонализация сайта: не упоминался | Квизы и опросы: не упоминался | ML рекомендации: не упоминался | Аналитика и A/B тесты: по базе — не упоминался, по ПЛ — не упоминался, по рекламе — не упоминался, A/B тесты — не упоминался</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>Клиент сформулировал цели.
 Проекты/задачи:
@@ -5236,17 +4865,17 @@
 - Низкая эффективность пушей при большом объёме отправок | Кто: Собственник</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>Собственник, Маркетолог</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>Стоимость: Клиент считает Mindbox дорогим для своего масштаба бизнеса. Названная цена Mindbox — ~150 тыс. руб./мес до НДС (~183 тыс. с НДС). Стоимость текущего стека не озвучена. Контекст: «нам дорого», «слишком маленькая компания, кто вообще столько платит» (конкретные суммы текущего стека не озвучены).</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>[Сценарии и триггеры] Рассылки отправляются полностью вручную, нет автоматизации
 «Мы отправляем рассылки вручную»
@@ -5258,70 +4887,70 @@
 «Мы сейчас пушей столько шлём, что мне кажется, у них там эффективность вообще хреновая»</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>2026-06-29T15:31:27Z</t>
         </is>
       </c>
-      <c r="P62" s="3" t="inlineStr">
+      <c r="P57" s="3" t="inlineStr">
         <is>
           <t>SS</t>
         </is>
       </c>
-      <c r="Q62" s="3" t="inlineStr">
+      <c r="Q57" s="3" t="inlineStr">
         <is>
           <t>Указана причина SS</t>
         </is>
       </c>
-      <c r="R62" s="3" t="inlineStr">
+      <c r="R57" s="3" t="inlineStr">
         <is>
           <t>Коммент пуст — по указанной причине/заметкам.</t>
         </is>
       </c>
-      <c r="S62" s="3" t="inlineStr">
+      <c r="S57" s="3" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="n">
+    <row r="58">
+      <c r="A58" t="n">
         <v>384741</v>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>https://mindbox.pipedrive.com/deal/384741</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>chicko.me Назначена встреча</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>Midmarket: выбрали конкурента, текущий стек или сделают сами – напиши кому в Коммент при проигрыше</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t xml:space="preserve">Работают на премиум бонусе, отказываются даже от приложения. Оптимизиуруют косты, пока не до перехода </t>
         </is>
       </c>
-      <c r="H63" t="n">
+      <c r="H58" t="n">
         <v>385</v>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
         <is>
           <t>CDP / база клиентов: Премиум бонус (в рамках ПЛ) | Email: используют, но не определили стек | SMS: не упоминался | Мессенджеры: планируют | Мобильные пуши / In-app: используют (через приложение, планируют отказ) | Чат-боты: планируют | Лояльность: Премиум бонус | Сценарии и триггеры: не упоминался | Персонализация сайта: не упоминался | Квизы и опросы: не упоминался | ML рекомендации: не упоминался | Аналитика и A/B тесты: по ПЛ — Премиум бонус (встроенная), по базе — не упоминался, по рекламе — не упоминался, A/B тесты — есть</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>Клиент сформулировал цели.
 Метрики:
@@ -5336,12 +4965,12 @@
 - Некорректная отчётность в личном кабинете Премиум бонус — ошибки при погружении в данные | Кто: Директор по маркетингу</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>Директор по маркетингу</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>[Лояльность] Премиум бонус покрывает базовые потребности по сегментации и начислению бонусов
 «Мы просто начисляем чекоины, конечно, мы работаем с сегментацией, да, и делаем, ну, это тоже все есть»
@@ -5350,7 +4979,7 @@
 Стоимость: Клиент считает Mindbox значительно дороже текущего стека. Минималка Mindbox озвучена как 183 тыс./мес. Кристина: «Да, тут можно даже не ставить встречу. Да, дорого» и «у нас просто прям другие условия... гораздо лояльнее». Конкретная стоимость текущего стека не озвучена.</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>[Аналитика и A/B тесты] Некорректная отчётность в личном кабинете Премиум бонус — ошибки при погружении в данные
 «у премиум-бонус есть минус, да, это вот как раз-таки непонятная отчётность, но там не то, чтобы она непонятная, она не совсем корректная в личном кабинете, да, и когда начинаешь погружаться, да, смотреть, выявляешь какие-то ошибки»
@@ -5362,65 +4991,65 @@
 «у нас нет коммуникации, потому что пользователь удалил приложение, да, если бы у него хотя бы валид был, то мы бы через валид как-то могли достучаться, но мы не можем достучаться через валид»</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>2026-06-24T15:28:17Z</t>
         </is>
       </c>
-      <c r="P63" s="3" t="inlineStr">
+      <c r="P58" s="3" t="inlineStr">
         <is>
           <t>Конкурент</t>
         </is>
       </c>
-      <c r="Q63" s="3" t="inlineStr">
+      <c r="Q58" s="3" t="inlineStr">
         <is>
           <t>Премиум Бонус (отказываются даже от приложения, оптимизируют затраты)</t>
         </is>
       </c>
-      <c r="R63" s="3" t="inlineStr">
+      <c r="R58" s="3" t="inlineStr">
         <is>
           <t>Коммент при проигрыше: «Работают на премиум бонусе, отказываются даже от приложения. Оптимизиуруют косты, пока не до перехода ».</t>
         </is>
       </c>
-      <c r="S63" s="3" t="inlineStr">
+      <c r="S58" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="n">
+    <row r="59">
+      <c r="A59" t="n">
         <v>384758</v>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>https://mindbox.pipedrive.com/deal/384758</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Сделка sad-i-ogorod.ru</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>Midmarket до встречи: неприоритетная для меня компания</t>
         </is>
       </c>
-      <c r="H64" t="n">
+      <c r="H59" t="n">
         <v>385</v>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
         <is>
           <t>CDP / база клиентов: не упоминался | Email: Sensei | SMS: не упоминался | Мессенджеры: не упоминался | Мобильные пуши / In-app: не упоминался | Чат-боты: не упоминался | Лояльность: планируют: In-house решение | Сценарии и триггеры: не упоминался | Персонализация сайта: не упоминался | Квизы и опросы: не упоминался | ML рекомендации: AnyQuery | Аналитика и A/B тесты: по базе — Sensei (встроенная), по ПЛ — не упоминался, по рекламе — не упоминался, A/B тесты — не упоминался</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>Клиент не сформулировал явных целей. Ниже фоновые проблемы и ограничения.
 Проекты/задачи:
@@ -5432,12 +5061,12 @@
 - Отсутствие бюджета в несезон (до октября), формирование бюджета начнётся в сентябре | Кто: интернет-маркетолог</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>Интернет-маркетолог</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>[Email] Sensei имеет неплохую встроенную аналитику
 «Это рассылки плюс внутренняя аналитика. У них там есть довольно неплохая.»
@@ -5446,7 +5075,7 @@
 Стоимость: клиент платит за текущий стек (Sensei + AnyQuery) ≈120–130 тыс. ₽/мес. Mindbox — конкретная цена не названа, но клиент считает её «очень сильно высокой» и неоднократно отказывался именно по ценовому фактору.</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>[Аналитика и A/B тесты] Нет атрибуции заказов из мобильного приложения — заказы обезличены, не привязаны к каналам привлечения
 «Мы, если видим заказы, то как бы условно обезличенные. То есть, мы не видим, к какому каналу этот заказ относится… именно функционала отслеживания, откуда этот заказ пришел, мы не видим.»
@@ -5454,302 +5083,196 @@
 «Она очень большая, но она очень старая.»</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>2026-06-30T08:41:29Z</t>
         </is>
       </c>
-      <c r="P64" s="3" t="inlineStr">
-        <is>
-          <t>Клиент перестал отвечать</t>
-        </is>
-      </c>
-      <c r="Q64" s="3" t="inlineStr">
-        <is>
-          <t>Проигрыш до встречи, нет ответа</t>
-        </is>
-      </c>
-      <c r="R64" s="3" t="inlineStr">
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>Попросили отложить</t>
+        </is>
+      </c>
+      <c r="Q59" s="3" t="inlineStr">
+        <is>
+          <t>Отложили</t>
+        </is>
+      </c>
+      <c r="R59" s="3" t="inlineStr">
+        <is>
+          <t>Уточнено вручную: попросили отложить.</t>
+        </is>
+      </c>
+      <c r="S59" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>385257</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>https://mindbox.pipedrive.com/deal/385257</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Сделка zvuk-b2b.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Midmarket: не нашел подходящей причины проигрыша – напиши свою в Коммент при проигрыше</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>сказали мб в 27 году будет больше задач, где нужна автоматизация и продолжим общение + скинули материалы</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>385</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>2026-06-23T11:41:26Z</t>
+        </is>
+      </c>
+      <c r="P60" s="3" t="inlineStr">
+        <is>
+          <t>Попросили отложить</t>
+        </is>
+      </c>
+      <c r="Q60" s="3" t="inlineStr">
+        <is>
+          <t>Задачи под автоматизацию появятся в 2027</t>
+        </is>
+      </c>
+      <c r="R60" s="3" t="inlineStr">
+        <is>
+          <t>Коммент при проигрыше: «сказали мб в 27 году будет больше задач, где нужна автоматизация и продолжим общение + скинули материалы».</t>
+        </is>
+      </c>
+      <c r="S60" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>385523</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>https://mindbox.pipedrive.com/deal/385523</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>белая-техника.рф</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Midmarket: SS, так как маленькая база</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>386</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>2026-06-26T08:30:29Z</t>
+        </is>
+      </c>
+      <c r="P61" s="3" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="Q61" s="3" t="inlineStr">
+        <is>
+          <t>Указана причина SS</t>
+        </is>
+      </c>
+      <c r="R61" s="3" t="inlineStr">
         <is>
           <t>Коммент пуст — по указанной причине/заметкам.</t>
         </is>
       </c>
-      <c r="S64" s="3" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>385257</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>https://mindbox.pipedrive.com/deal/385257</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Сделка zvuk-b2b.com</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
+      <c r="S61" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>386653</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>https://mindbox.pipedrive.com/deal/386653</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>kassy.ru</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
         <is>
           <t>Midmarket: не нашел подходящей причины проигрыша – напиши свою в Коммент при проигрыше</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>сказали мб в 27 году будет больше задач, где нужна автоматизация и продолжим общение + скинули материалы</t>
-        </is>
-      </c>
-      <c r="H65" t="n">
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Отложили</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
         <v>385</v>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>2026-06-23T11:41:26Z</t>
-        </is>
-      </c>
-      <c r="P65" s="3" t="inlineStr">
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>2026-06-30T10:36:00Z</t>
+        </is>
+      </c>
+      <c r="P62" s="3" t="inlineStr">
         <is>
           <t>Попросили отложить</t>
         </is>
       </c>
-      <c r="Q65" s="3" t="inlineStr">
-        <is>
-          <t>Задачи под автоматизацию появятся в 2027</t>
-        </is>
-      </c>
-      <c r="R65" s="3" t="inlineStr">
-        <is>
-          <t>Коммент при проигрыше: «сказали мб в 27 году будет больше задач, где нужна автоматизация и продолжим общение + скинули материалы».</t>
-        </is>
-      </c>
-      <c r="S65" s="3" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>385523</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>https://mindbox.pipedrive.com/deal/385523</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>белая-техника.рф</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Midmarket: SS, так как маленькая база</t>
-        </is>
-      </c>
-      <c r="H66" t="n">
-        <v>386</v>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>2026-06-26T08:30:29Z</t>
-        </is>
-      </c>
-      <c r="P66" s="3" t="inlineStr">
-        <is>
-          <t>SS</t>
-        </is>
-      </c>
-      <c r="Q66" s="3" t="inlineStr">
-        <is>
-          <t>Указана причина SS</t>
-        </is>
-      </c>
-      <c r="R66" s="3" t="inlineStr">
-        <is>
-          <t>Коммент пуст — по указанной причине/заметкам.</t>
-        </is>
-      </c>
-      <c r="S66" s="3" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>385532</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>https://mindbox.pipedrive.com/deal/385532</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>centek.ru</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>MDR: тест или дубль</t>
-        </is>
-      </c>
-      <c r="H67" t="n">
-        <v>385</v>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>2026-06-24T06:44:29Z</t>
-        </is>
-      </c>
-      <c r="P67" s="3" t="inlineStr">
-        <is>
-          <t>Нецелевой</t>
-        </is>
-      </c>
-      <c r="Q67" s="3" t="inlineStr">
-        <is>
-          <t>Тест/дубль (MDR)</t>
-        </is>
-      </c>
-      <c r="R67" s="3" t="inlineStr">
-        <is>
-          <t>Коммент пуст — по указанной причине/заметкам.</t>
-        </is>
-      </c>
-      <c r="S67" s="3" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>385533</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>https://mindbox.pipedrive.com/deal/385533</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>centek.ru</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>MDR: тест или дубль</t>
-        </is>
-      </c>
-      <c r="H68" t="n">
-        <v>449</v>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>2026-06-24T06:32:55Z</t>
-        </is>
-      </c>
-      <c r="P68" s="3" t="inlineStr">
-        <is>
-          <t>Нецелевой</t>
-        </is>
-      </c>
-      <c r="Q68" s="3" t="inlineStr">
-        <is>
-          <t>Тест/дубль (MDR)</t>
-        </is>
-      </c>
-      <c r="R68" s="3" t="inlineStr">
-        <is>
-          <t>Коммент пуст — по указанной причине/заметкам.</t>
-        </is>
-      </c>
-      <c r="S68" s="3" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>386653</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>https://mindbox.pipedrive.com/deal/386653</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>kassy.ru</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Midmarket: не нашел подходящей причины проигрыша – напиши свою в Коммент при проигрыше</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
+      <c r="Q62" s="3" t="inlineStr">
         <is>
           <t>Отложили</t>
         </is>
       </c>
-      <c r="H69" t="n">
-        <v>385</v>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>2026-06-30T10:36:00Z</t>
-        </is>
-      </c>
-      <c r="P69" s="3" t="inlineStr">
-        <is>
-          <t>Попросили отложить</t>
-        </is>
-      </c>
-      <c r="Q69" s="3" t="inlineStr">
-        <is>
-          <t>Отложили</t>
-        </is>
-      </c>
-      <c r="R69" s="3" t="inlineStr">
+      <c r="R62" s="3" t="inlineStr">
         <is>
           <t>Коммент при проигрыше: «Отложили».</t>
         </is>
       </c>
-      <c r="S69" s="3" t="inlineStr">
+      <c r="S62" s="3" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
